--- a/database/event/2568/event_2568_evp_summary.xlsx
+++ b/database/event/2568/event_2568_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.0021</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0914</v>
+        <v>2.0342</v>
       </c>
       <c r="E2" t="n">
         <v>6.2201</v>
@@ -548,7 +548,7 @@
         <v>0.9042</v>
       </c>
       <c r="D3" t="n">
-        <v>1.846</v>
+        <v>1.7922</v>
       </c>
       <c r="E3" t="n">
         <v>5.6126</v>
@@ -584,127 +584,127 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.0906</v>
+        <v>5.2467</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.8452</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6351</v>
+        <v>1.6464</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0906</v>
+        <v>5.2467</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2687</v>
+        <v>3.1097</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8219</v>
+        <v>2.137</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6135</v>
+        <v>3.1097</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7394</v>
+        <v>2.5205</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8219</v>
+        <v>2.137</v>
       </c>
       <c r="K4" t="n">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="L4" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="M4" t="n">
-        <v>4.5613</v>
+        <v>4.657500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>231</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6853</v>
+        <v>5.0906</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7548</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4714</v>
+        <v>1.5842</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6853</v>
+        <v>5.0906</v>
       </c>
       <c r="F5" t="n">
-        <v>2.854</v>
+        <v>4.2687</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8313</v>
+        <v>0.8219</v>
       </c>
       <c r="H5" t="n">
-        <v>2.854</v>
+        <v>4.6135</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3132</v>
+        <v>3.7394</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8313</v>
+        <v>0.8219</v>
       </c>
       <c r="K5" t="n">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="L5" t="n">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="M5" t="n">
-        <v>4.1445</v>
+        <v>4.5613</v>
       </c>
       <c r="N5" t="n">
-        <v>253</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5918</v>
+        <v>4.7623</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7397</v>
+        <v>0.7672</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4336</v>
+        <v>1.4534</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5918</v>
+        <v>4.7623</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4549</v>
+        <v>3.0282</v>
       </c>
       <c r="G6" t="n">
-        <v>2.137</v>
+        <v>1.7341</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4549</v>
+        <v>3.0282</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9897</v>
+        <v>2.4544</v>
       </c>
       <c r="J6" t="n">
-        <v>2.137</v>
+        <v>1.7341</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -713,7 +713,7 @@
         <v>105</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1267</v>
+        <v>4.1885</v>
       </c>
       <c r="N6" t="n">
         <v>155</v>
@@ -722,47 +722,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1423</v>
+        <v>4.6853</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6673</v>
+        <v>0.7548</v>
       </c>
       <c r="D7" t="n">
-        <v>1.252</v>
+        <v>1.4227</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1423</v>
+        <v>4.6853</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4082</v>
+        <v>2.854</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7341</v>
+        <v>1.8313</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4082</v>
+        <v>2.854</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9519</v>
+        <v>2.3132</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7341</v>
+        <v>1.8313</v>
       </c>
       <c r="K7" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="L7" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="M7" t="n">
-        <v>3.686</v>
+        <v>4.1445</v>
       </c>
       <c r="N7" t="n">
-        <v>155</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8">
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9468</v>
+        <v>3.512</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4747</v>
+        <v>0.5658</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7691</v>
+        <v>0.9553</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9468</v>
+        <v>3.512</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4383</v>
+        <v>3.0035</v>
       </c>
       <c r="G8" t="n">
         <v>0.5085</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4383</v>
+        <v>3.0035</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9763</v>
+        <v>2.4344</v>
       </c>
       <c r="J8" t="n">
         <v>0.5085</v>
@@ -805,7 +805,7 @@
         <v>76</v>
       </c>
       <c r="M8" t="n">
-        <v>2.4848</v>
+        <v>2.9429</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2931</v>
+        <v>2.8167</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3694</v>
+        <v>0.4538</v>
       </c>
       <c r="D9" t="n">
-        <v>0.505</v>
+        <v>0.6783</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2931</v>
+        <v>2.8167</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2228</v>
+        <v>2.7464</v>
       </c>
       <c r="G9" t="n">
         <v>0.0703</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2228</v>
+        <v>2.7464</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8016</v>
+        <v>2.226</v>
       </c>
       <c r="J9" t="n">
         <v>0.0703</v>
@@ -851,7 +851,7 @@
         <v>76</v>
       </c>
       <c r="M9" t="n">
-        <v>1.8719</v>
+        <v>2.2963</v>
       </c>
       <c r="N9" t="n">
         <v>121</v>
@@ -870,7 +870,7 @@
         <v>0.3568</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4732</v>
+        <v>0.4383</v>
       </c>
       <c r="E10" t="n">
         <v>2.2145</v>
@@ -916,7 +916,7 @@
         <v>0.3529</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4636</v>
+        <v>0.4288</v>
       </c>
       <c r="E11" t="n">
         <v>2.1905</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7706</v>
+        <v>2.0464</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2852</v>
+        <v>0.3297</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2939</v>
+        <v>0.3714</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7706</v>
+        <v>2.0464</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7706</v>
+        <v>2.0464</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7706</v>
+        <v>2.0464</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7706</v>
+        <v>2.0464</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7706</v>
+        <v>2.0464</v>
       </c>
       <c r="N12" t="n">
         <v>104</v>
@@ -998,170 +998,170 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>devoduvek</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.3563</v>
+        <v>1.8754</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2185</v>
+        <v>0.3021</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1266</v>
+        <v>0.3032</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3563</v>
+        <v>1.8754</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9086</v>
+        <v>2.8754</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4477</v>
+        <v>-1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9086</v>
+        <v>2.8754</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7364000000000001</v>
+        <v>2.3306</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4477</v>
+        <v>-1</v>
       </c>
       <c r="K13" t="n">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="L13" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1841</v>
+        <v>1.3306</v>
       </c>
       <c r="N13" t="n">
-        <v>231</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>devoduvek</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.3247</v>
+        <v>1.3563</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2134</v>
+        <v>0.2185</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1138</v>
+        <v>0.0964</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3247</v>
+        <v>1.3563</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3247</v>
+        <v>0.9086</v>
       </c>
       <c r="G14" t="n">
-        <v>-1</v>
+        <v>0.4477</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3247</v>
+        <v>0.9086</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8843</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-1</v>
+        <v>0.4477</v>
       </c>
       <c r="K14" t="n">
-        <v>45</v>
+        <v>178</v>
       </c>
       <c r="L14" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8843000000000001</v>
+        <v>1.1841</v>
       </c>
       <c r="N14" t="n">
-        <v>121</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1079</v>
+        <v>1.2769</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1785</v>
+        <v>0.2057</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0262</v>
+        <v>0.0648</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1079</v>
+        <v>1.2769</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1079</v>
+        <v>2.7208</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-1.4439</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1079</v>
+        <v>2.7208</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1079</v>
+        <v>2.2053</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-1.4439</v>
       </c>
       <c r="K15" t="n">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1079</v>
+        <v>0.7613999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>115</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9813</v>
+        <v>1.1079</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1581</v>
+        <v>0.1785</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0249</v>
+        <v>-0.0025</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9813</v>
+        <v>1.1079</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9813</v>
+        <v>1.1079</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9813</v>
+        <v>1.1079</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9813</v>
+        <v>1.1079</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9813</v>
+        <v>1.1079</v>
       </c>
       <c r="N16" t="n">
         <v>115</v>
@@ -1182,185 +1182,185 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.897</v>
+        <v>1.0072</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1445</v>
+        <v>0.1623</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.059</v>
+        <v>-0.0426</v>
       </c>
       <c r="E17" t="n">
-        <v>0.897</v>
+        <v>1.0072</v>
       </c>
       <c r="F17" t="n">
-        <v>0.897</v>
+        <v>1.0072</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.897</v>
+        <v>1.0072</v>
       </c>
       <c r="I17" t="n">
-        <v>0.897</v>
+        <v>1.0072</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.897</v>
+        <v>1.0072</v>
       </c>
       <c r="N17" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7188</v>
+        <v>0.9813</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1158</v>
+        <v>0.1581</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.131</v>
+        <v>-0.053</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7188</v>
+        <v>0.9813</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1627</v>
+        <v>0.9813</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4439</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1627</v>
+        <v>0.9813</v>
       </c>
       <c r="I18" t="n">
-        <v>1.753</v>
+        <v>0.9813</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.4439</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="L18" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3090999999999999</v>
+        <v>0.9813</v>
       </c>
       <c r="N18" t="n">
-        <v>155</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.897</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1133</v>
+        <v>0.1445</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1373</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.897</v>
       </c>
       <c r="F19" t="n">
-        <v>1.654</v>
+        <v>0.897</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9509</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.654</v>
+        <v>0.897</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3406</v>
+        <v>0.897</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9509</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>178</v>
+        <v>115</v>
       </c>
       <c r="L19" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3897</v>
+        <v>0.897</v>
       </c>
       <c r="N19" t="n">
-        <v>231</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.67</v>
+        <v>0.7516</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1079</v>
+        <v>0.1211</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1507</v>
+        <v>-0.1445</v>
       </c>
       <c r="E20" t="n">
-        <v>0.67</v>
+        <v>0.7516</v>
       </c>
       <c r="F20" t="n">
-        <v>0.67</v>
+        <v>0.7516</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.67</v>
+        <v>0.7516</v>
       </c>
       <c r="I20" t="n">
-        <v>0.67</v>
+        <v>0.7516</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.67</v>
+        <v>0.7516</v>
       </c>
       <c r="N20" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6262</v>
+        <v>0.7125</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1009</v>
+        <v>0.1148</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1684</v>
+        <v>-0.1601</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6262</v>
+        <v>0.7125</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6262</v>
+        <v>0.7125</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6262</v>
+        <v>0.7125</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6262</v>
+        <v>0.7125</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6262</v>
+        <v>0.7125</v>
       </c>
       <c r="N21" t="n">
         <v>104</v>
@@ -1412,219 +1412,219 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2976</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0479</v>
+        <v>0.1133</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3011</v>
+        <v>-0.1638</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2976</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2976</v>
+        <v>1.654</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.9509</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2976</v>
+        <v>1.654</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2976</v>
+        <v>1.3406</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.9509</v>
       </c>
       <c r="K22" t="n">
-        <v>108</v>
+        <v>178</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2976</v>
+        <v>0.3897</v>
       </c>
       <c r="N22" t="n">
-        <v>108</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2813</v>
+        <v>0.2976</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0453</v>
+        <v>0.0479</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3077</v>
+        <v>-0.3253</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2813</v>
+        <v>0.2976</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2813</v>
+        <v>0.2976</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2813</v>
+        <v>0.2976</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2813</v>
+        <v>0.2976</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2813</v>
+        <v>0.2976</v>
       </c>
       <c r="N23" t="n">
-        <v>71</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SicK</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2693</v>
+        <v>0.2813</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0434</v>
+        <v>0.0453</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3126</v>
+        <v>-0.3318</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2693</v>
+        <v>0.2813</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9093</v>
+        <v>0.2813</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.64</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9093</v>
+        <v>0.2813</v>
       </c>
       <c r="I24" t="n">
-        <v>0.737</v>
+        <v>0.2813</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.64</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>178</v>
+        <v>71</v>
       </c>
       <c r="L24" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.09699999999999998</v>
+        <v>0.2813</v>
       </c>
       <c r="N24" t="n">
-        <v>231</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>SicK</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.012</v>
+        <v>0.2693</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0019</v>
+        <v>0.0434</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4165</v>
+        <v>-0.3366</v>
       </c>
       <c r="E25" t="n">
-        <v>0.012</v>
+        <v>0.2693</v>
       </c>
       <c r="F25" t="n">
-        <v>0.012</v>
+        <v>0.9093</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.64</v>
       </c>
       <c r="H25" t="n">
-        <v>0.012</v>
+        <v>0.9093</v>
       </c>
       <c r="I25" t="n">
-        <v>0.012</v>
+        <v>0.737</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.64</v>
       </c>
       <c r="K25" t="n">
-        <v>71</v>
+        <v>178</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M25" t="n">
-        <v>0.012</v>
+        <v>0.09699999999999998</v>
       </c>
       <c r="N25" t="n">
-        <v>71</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0056</v>
+        <v>0.1512</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0009</v>
+        <v>0.0244</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4236</v>
+        <v>-0.3837</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0056</v>
+        <v>0.1512</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9944</v>
+        <v>0.7058</v>
       </c>
       <c r="G26" t="n">
-        <v>-1</v>
+        <v>-0.5546</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9944</v>
+        <v>0.7058</v>
       </c>
       <c r="I26" t="n">
-        <v>0.806</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-1</v>
+        <v>-0.5546</v>
       </c>
       <c r="K26" t="n">
         <v>45</v>
@@ -1633,7 +1633,7 @@
         <v>76</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.194</v>
+        <v>0.01750000000000007</v>
       </c>
       <c r="N26" t="n">
         <v>121</v>
@@ -1642,35 +1642,35 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0299</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0048</v>
+        <v>0.0146</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4334</v>
+        <v>-0.4079</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0299</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5247000000000001</v>
+        <v>1.0904</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.5546</v>
+        <v>-1</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5247000000000001</v>
+        <v>1.0904</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4253</v>
+        <v>0.8838</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.5546</v>
+        <v>-1</v>
       </c>
       <c r="K27" t="n">
         <v>45</v>
@@ -1679,7 +1679,7 @@
         <v>76</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1293</v>
+        <v>-0.1162</v>
       </c>
       <c r="N27" t="n">
         <v>121</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0302</v>
+        <v>0.012</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0049</v>
+        <v>0.0019</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4336</v>
+        <v>-0.4391</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0302</v>
+        <v>0.012</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.027</v>
+        <v>0.012</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0032</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.027</v>
+        <v>0.012</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0219</v>
+        <v>0.012</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.0032</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="L28" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0251</v>
+        <v>0.012</v>
       </c>
       <c r="N28" t="n">
-        <v>155</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0973</v>
+        <v>-0.0302</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0157</v>
+        <v>-0.0049</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4607</v>
+        <v>-0.4559</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0973</v>
+        <v>-0.0302</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0973</v>
+        <v>-0.027</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.0032</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0973</v>
+        <v>-0.027</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0973</v>
+        <v>-0.0219</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.0032</v>
       </c>
       <c r="K29" t="n">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0973</v>
+        <v>-0.0251</v>
       </c>
       <c r="N29" t="n">
-        <v>108</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30">
@@ -1790,7 +1790,7 @@
         <v>-0.0276</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4905</v>
+        <v>-0.5121</v>
       </c>
       <c r="E30" t="n">
         <v>-0.1712</v>
@@ -1836,7 +1836,7 @@
         <v>-0.0282</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.492</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="E31" t="n">
         <v>-0.1748</v>
@@ -1882,7 +1882,7 @@
         <v>-0.0491</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5445</v>
+        <v>-0.5653</v>
       </c>
       <c r="E32" t="n">
         <v>-0.3048</v>
@@ -1928,7 +1928,7 @@
         <v>-0.0536</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.5766</v>
       </c>
       <c r="E33" t="n">
         <v>-0.333</v>
@@ -1974,7 +1974,7 @@
         <v>-0.0639</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.5817</v>
+        <v>-0.602</v>
       </c>
       <c r="E34" t="n">
         <v>-0.3969</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7492</v>
+        <v>-0.4219</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1207</v>
+        <v>-0.068</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.724</v>
+        <v>-0.612</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7492</v>
+        <v>-0.4219</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7492</v>
+        <v>-0.4219</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7492</v>
+        <v>-0.4219</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7492</v>
+        <v>-0.4219</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7492</v>
+        <v>-0.4219</v>
       </c>
       <c r="N35" t="n">
         <v>104</v>
@@ -2056,32 +2056,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7764</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1251</v>
+        <v>-0.1217</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.735</v>
+        <v>-0.7449</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7764</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7764</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7764</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7764</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7764</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="N36" t="n">
         <v>108</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9196</v>
+        <v>-0.7764</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1481</v>
+        <v>-0.1251</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.7929</v>
+        <v>-0.7532</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9196</v>
+        <v>-0.7764</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9196</v>
+        <v>-0.7764</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9196</v>
+        <v>-0.7764</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9196</v>
+        <v>-0.7764</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9196</v>
+        <v>-0.7764</v>
       </c>
       <c r="N37" t="n">
-        <v>71</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0949</v>
+        <v>-0.9196</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1764</v>
+        <v>-0.1481</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8637</v>
+        <v>-0.8103</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0949</v>
+        <v>-0.9196</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0949</v>
+        <v>-0.9196</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0949</v>
+        <v>-0.9196</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0949</v>
+        <v>-0.9196</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0949</v>
+        <v>-0.9196</v>
       </c>
       <c r="N38" t="n">
-        <v>108</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39">
@@ -2204,7 +2204,7 @@
         <v>-0.2401</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0233</v>
+        <v>-1.0376</v>
       </c>
       <c r="E39" t="n">
         <v>-1.4901</v>
@@ -2250,7 +2250,7 @@
         <v>-0.3133</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2071</v>
+        <v>-1.2188</v>
       </c>
       <c r="E40" t="n">
         <v>-1.9449</v>
@@ -2296,7 +2296,7 @@
         <v>-0.5649</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.838</v>
+        <v>-1.841</v>
       </c>
       <c r="E41" t="n">
         <v>-3.5068</v>

--- a/database/event/2568/event_2568_evp_summary.xlsx
+++ b/database/event/2568/event_2568_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2201</v>
+        <v>6.376</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0021</v>
+        <v>1.0272</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0342</v>
+        <v>2.2404</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2201</v>
+        <v>6.376</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4028</v>
+        <v>2.3321</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8173</v>
+        <v>4.0439</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4028</v>
+        <v>2.7304</v>
       </c>
       <c r="I2" t="n">
-        <v>1.137</v>
+        <v>1.4197</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8173</v>
+        <v>4.0439</v>
       </c>
       <c r="K2" t="n">
         <v>125</v>
@@ -529,7 +529,7 @@
         <v>128</v>
       </c>
       <c r="M2" t="n">
-        <v>5.9543</v>
+        <v>5.4636</v>
       </c>
       <c r="N2" t="n">
         <v>253</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.6126</v>
+        <v>5.4469</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9042</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7922</v>
+        <v>1.821</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6126</v>
+        <v>5.4469</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2053</v>
+        <v>3.0684</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4073</v>
+        <v>2.3785</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2053</v>
+        <v>5.3247</v>
       </c>
       <c r="I3" t="n">
-        <v>2.598</v>
+        <v>2.7686</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4073</v>
+        <v>2.3785</v>
       </c>
       <c r="K3" t="n">
         <v>125</v>
@@ -575,7 +575,7 @@
         <v>128</v>
       </c>
       <c r="M3" t="n">
-        <v>5.0053</v>
+        <v>5.1471</v>
       </c>
       <c r="N3" t="n">
         <v>253</v>
@@ -584,185 +584,185 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2467</v>
+        <v>4.7382</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8452</v>
+        <v>0.7633</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6464</v>
+        <v>1.501</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2467</v>
+        <v>4.7382</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1097</v>
+        <v>3.9142</v>
       </c>
       <c r="G4" t="n">
-        <v>2.137</v>
+        <v>0.824</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1097</v>
+        <v>8.3048</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5205</v>
+        <v>4.3181</v>
       </c>
       <c r="J4" t="n">
-        <v>2.137</v>
+        <v>0.824</v>
       </c>
       <c r="K4" t="n">
-        <v>50</v>
+        <v>178</v>
       </c>
       <c r="L4" t="n">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="M4" t="n">
-        <v>4.657500000000001</v>
+        <v>5.1421</v>
       </c>
       <c r="N4" t="n">
-        <v>155</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0906</v>
+        <v>4.5567</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.7341</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5842</v>
+        <v>1.4191</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0906</v>
+        <v>4.5567</v>
       </c>
       <c r="F5" t="n">
-        <v>4.2687</v>
+        <v>2.8136</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8219</v>
+        <v>1.7431</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6135</v>
+        <v>4.4271</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7394</v>
+        <v>2.3019</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8219</v>
+        <v>1.7431</v>
       </c>
       <c r="K5" t="n">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="L5" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5613</v>
+        <v>4.045</v>
       </c>
       <c r="N5" t="n">
-        <v>231</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7623</v>
+        <v>4.4018</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7672</v>
+        <v>0.7091</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4534</v>
+        <v>1.3492</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7623</v>
+        <v>4.4018</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0282</v>
+        <v>2.9136</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7341</v>
+        <v>1.4882</v>
       </c>
       <c r="H6" t="n">
-        <v>3.0282</v>
+        <v>4.7793</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4544</v>
+        <v>2.485</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7341</v>
+        <v>1.4882</v>
       </c>
       <c r="K6" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="L6" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1885</v>
+        <v>3.9732</v>
       </c>
       <c r="N6" t="n">
-        <v>155</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6853</v>
+        <v>4.3081</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7548</v>
+        <v>0.694</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4227</v>
+        <v>1.3069</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6853</v>
+        <v>4.3081</v>
       </c>
       <c r="F7" t="n">
-        <v>2.854</v>
+        <v>2.8124</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8313</v>
+        <v>1.4957</v>
       </c>
       <c r="H7" t="n">
-        <v>2.854</v>
+        <v>4.4227</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3132</v>
+        <v>2.2996</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8313</v>
+        <v>1.4957</v>
       </c>
       <c r="K7" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="L7" t="n">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1445</v>
+        <v>3.7953</v>
       </c>
       <c r="N7" t="n">
-        <v>253</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.512</v>
+        <v>3.2971</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5658</v>
+        <v>0.5312</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9553</v>
+        <v>0.8505</v>
       </c>
       <c r="E8" t="n">
-        <v>3.512</v>
+        <v>3.2971</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0035</v>
+        <v>2.8291</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5085</v>
+        <v>0.468</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0035</v>
+        <v>4.4817</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4344</v>
+        <v>2.3303</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5085</v>
+        <v>0.468</v>
       </c>
       <c r="K8" t="n">
         <v>45</v>
@@ -805,7 +805,7 @@
         <v>76</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9429</v>
+        <v>2.7983</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8167</v>
+        <v>2.7649</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4538</v>
+        <v>0.4454</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6783</v>
+        <v>0.6102</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8167</v>
+        <v>2.7649</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7464</v>
+        <v>2.712</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0703</v>
+        <v>0.0529</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7464</v>
+        <v>4.069</v>
       </c>
       <c r="I9" t="n">
-        <v>2.226</v>
+        <v>2.1157</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0703</v>
+        <v>0.0529</v>
       </c>
       <c r="K9" t="n">
         <v>45</v>
@@ -851,7 +851,7 @@
         <v>76</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2963</v>
+        <v>2.1686</v>
       </c>
       <c r="N9" t="n">
         <v>121</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2145</v>
+        <v>2.6803</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3568</v>
+        <v>0.4318</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4383</v>
+        <v>0.572</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2145</v>
+        <v>2.6803</v>
       </c>
       <c r="F10" t="n">
-        <v>2.747</v>
+        <v>2.9498</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5325</v>
+        <v>-0.2695</v>
       </c>
       <c r="H10" t="n">
-        <v>2.747</v>
+        <v>4.907</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2265</v>
+        <v>2.5514</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5325</v>
+        <v>-0.2695</v>
       </c>
       <c r="K10" t="n">
         <v>125</v>
@@ -897,7 +897,7 @@
         <v>128</v>
       </c>
       <c r="M10" t="n">
-        <v>1.694</v>
+        <v>2.2819</v>
       </c>
       <c r="N10" t="n">
         <v>253</v>
@@ -906,47 +906,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>devoduvek</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1905</v>
+        <v>2.6081</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3529</v>
+        <v>0.4202</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4288</v>
+        <v>0.5394</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1905</v>
+        <v>2.6081</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9906</v>
+        <v>2.1832</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1811</v>
+        <v>0.4249</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9906</v>
+        <v>2.206</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8028999999999999</v>
+        <v>1.147</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1811</v>
+        <v>0.4249</v>
       </c>
       <c r="K11" t="n">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="L11" t="n">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="M11" t="n">
-        <v>2.3782</v>
+        <v>1.5719</v>
       </c>
       <c r="N11" t="n">
-        <v>253</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0464</v>
+        <v>2.4852</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3297</v>
+        <v>0.4004</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3714</v>
+        <v>0.4839</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0464</v>
+        <v>2.4852</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0464</v>
+        <v>2.4852</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0464</v>
+        <v>2.4852</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0464</v>
+        <v>2.4852</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0464</v>
+        <v>2.4852</v>
       </c>
       <c r="N12" t="n">
         <v>104</v>
@@ -998,81 +998,81 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.8754</v>
+        <v>2.2762</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3021</v>
+        <v>0.3667</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3032</v>
+        <v>0.3896</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8754</v>
+        <v>2.2762</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8754</v>
+        <v>-0.5854</v>
       </c>
       <c r="G13" t="n">
-        <v>-1</v>
+        <v>2.8616</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8754</v>
+        <v>-0.5854</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3306</v>
+        <v>-0.3044</v>
       </c>
       <c r="J13" t="n">
-        <v>-1</v>
+        <v>2.8616</v>
       </c>
       <c r="K13" t="n">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="L13" t="n">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3306</v>
+        <v>2.5572</v>
       </c>
       <c r="N13" t="n">
-        <v>121</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>devoduvek</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.3563</v>
+        <v>2.0944</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2185</v>
+        <v>0.3374</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0964</v>
+        <v>0.3075</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3563</v>
+        <v>2.0944</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9086</v>
+        <v>2.7137</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4477</v>
+        <v>-0.6193</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9086</v>
+        <v>4.075</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7364000000000001</v>
+        <v>2.1188</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4477</v>
+        <v>-0.6193</v>
       </c>
       <c r="K14" t="n">
         <v>178</v>
@@ -1081,7 +1081,7 @@
         <v>53</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1841</v>
+        <v>1.4995</v>
       </c>
       <c r="N14" t="n">
         <v>231</v>
@@ -1090,921 +1090,921 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.2769</v>
+        <v>1.9836</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2057</v>
+        <v>0.3196</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0648</v>
+        <v>0.2575</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2769</v>
+        <v>1.9836</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7208</v>
+        <v>2.7926</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4439</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7208</v>
+        <v>4.3531</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2053</v>
+        <v>2.2634</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.4439</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L15" t="n">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7613999999999999</v>
+        <v>1.4544</v>
       </c>
       <c r="N15" t="n">
-        <v>155</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1079</v>
+        <v>1.4715</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1785</v>
+        <v>0.2371</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0025</v>
+        <v>0.0263</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1079</v>
+        <v>1.4715</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1079</v>
+        <v>1.4715</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1079</v>
+        <v>1.4715</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1079</v>
+        <v>1.4715</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1079</v>
+        <v>1.4715</v>
       </c>
       <c r="N16" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>SicK</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.0072</v>
+        <v>1.4146</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1623</v>
+        <v>0.2279</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0426</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0072</v>
+        <v>1.4146</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0072</v>
+        <v>1.8259</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.4113</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0072</v>
+        <v>1.8259</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0072</v>
+        <v>0.9494</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.4113</v>
       </c>
       <c r="K17" t="n">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0072</v>
+        <v>0.5381</v>
       </c>
       <c r="N17" t="n">
-        <v>104</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9813</v>
+        <v>1.3424</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1581</v>
+        <v>0.2163</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.053</v>
+        <v>-0.032</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9813</v>
+        <v>1.3424</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9813</v>
+        <v>2.6417</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-1.2993</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9813</v>
+        <v>3.8214</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9813</v>
+        <v>1.987</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-1.2993</v>
       </c>
       <c r="K18" t="n">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9813</v>
+        <v>0.6877000000000002</v>
       </c>
       <c r="N18" t="n">
-        <v>115</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.897</v>
+        <v>1.2408</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1445</v>
+        <v>0.1999</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0779</v>
       </c>
       <c r="E19" t="n">
-        <v>0.897</v>
+        <v>1.2408</v>
       </c>
       <c r="F19" t="n">
-        <v>0.897</v>
+        <v>2.0988</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.858</v>
       </c>
       <c r="H19" t="n">
-        <v>0.897</v>
+        <v>2.0988</v>
       </c>
       <c r="I19" t="n">
-        <v>0.897</v>
+        <v>1.0913</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.858</v>
       </c>
       <c r="K19" t="n">
-        <v>115</v>
+        <v>45</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M19" t="n">
-        <v>0.897</v>
+        <v>0.2333</v>
       </c>
       <c r="N19" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7516</v>
+        <v>1.1217</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1211</v>
+        <v>0.1807</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1445</v>
+        <v>-0.1316</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7516</v>
+        <v>1.1217</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7516</v>
+        <v>1.1217</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7516</v>
+        <v>1.1217</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7516</v>
+        <v>1.1217</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7516</v>
+        <v>1.1217</v>
       </c>
       <c r="N20" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7125</v>
+        <v>1.1129</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1148</v>
+        <v>0.1793</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1601</v>
+        <v>-0.1356</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7125</v>
+        <v>1.1129</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7125</v>
+        <v>1.1129</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7125</v>
+        <v>1.1129</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7125</v>
+        <v>1.1129</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7125</v>
+        <v>1.1129</v>
       </c>
       <c r="N21" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7030999999999999</v>
+        <v>1.0197</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1133</v>
+        <v>0.1643</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1638</v>
+        <v>-0.1777</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7030999999999999</v>
+        <v>1.0197</v>
       </c>
       <c r="F22" t="n">
-        <v>1.654</v>
+        <v>1.397</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9509</v>
+        <v>-0.3773</v>
       </c>
       <c r="H22" t="n">
-        <v>1.654</v>
+        <v>1.397</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3406</v>
+        <v>0.7264</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9509</v>
+        <v>-0.3773</v>
       </c>
       <c r="K22" t="n">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="L22" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3897</v>
+        <v>0.3491</v>
       </c>
       <c r="N22" t="n">
-        <v>231</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2976</v>
+        <v>1.0119</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0479</v>
+        <v>0.163</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3253</v>
+        <v>-0.1812</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2976</v>
+        <v>1.0119</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2976</v>
+        <v>1.0119</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2976</v>
+        <v>1.0119</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2976</v>
+        <v>1.0119</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2976</v>
+        <v>1.0119</v>
       </c>
       <c r="N23" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2813</v>
+        <v>0.9134</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0453</v>
+        <v>0.1471</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3318</v>
+        <v>-0.2257</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2813</v>
+        <v>0.9134</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2813</v>
+        <v>0.9134</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2813</v>
+        <v>0.9134</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2813</v>
+        <v>0.9134</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2813</v>
+        <v>0.9134</v>
       </c>
       <c r="N24" t="n">
-        <v>71</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SicK</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2693</v>
+        <v>0.7809</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0434</v>
+        <v>0.1258</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3366</v>
+        <v>-0.2855</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2693</v>
+        <v>0.7809</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9093</v>
+        <v>0.7809</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.64</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9093</v>
+        <v>0.7809</v>
       </c>
       <c r="I25" t="n">
-        <v>0.737</v>
+        <v>0.7809</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.64</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="L25" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.09699999999999998</v>
+        <v>0.7809</v>
       </c>
       <c r="N25" t="n">
-        <v>231</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1512</v>
+        <v>0.6123</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0244</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3837</v>
+        <v>-0.3616</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1512</v>
+        <v>0.6123</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7058</v>
+        <v>0.6123</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.5546</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7058</v>
+        <v>0.6123</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.6123</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.5546</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="L26" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.01750000000000007</v>
+        <v>0.6123</v>
       </c>
       <c r="N26" t="n">
-        <v>121</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.496</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0146</v>
+        <v>0.0799</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4079</v>
+        <v>-0.4141</v>
       </c>
       <c r="E27" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.496</v>
       </c>
       <c r="F27" t="n">
-        <v>1.0904</v>
+        <v>0.496</v>
       </c>
       <c r="G27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.0904</v>
+        <v>0.496</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8838</v>
+        <v>0.496</v>
       </c>
       <c r="J27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="L27" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1162</v>
+        <v>0.496</v>
       </c>
       <c r="N27" t="n">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.012</v>
+        <v>0.3942</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0019</v>
+        <v>0.0635</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4391</v>
+        <v>-0.4601</v>
       </c>
       <c r="E28" t="n">
-        <v>0.012</v>
+        <v>0.3942</v>
       </c>
       <c r="F28" t="n">
-        <v>0.012</v>
+        <v>0.1267</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.2675</v>
       </c>
       <c r="H28" t="n">
-        <v>0.012</v>
+        <v>0.1267</v>
       </c>
       <c r="I28" t="n">
-        <v>0.012</v>
+        <v>0.0659</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.2675</v>
       </c>
       <c r="K28" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M28" t="n">
-        <v>0.012</v>
+        <v>0.3334</v>
       </c>
       <c r="N28" t="n">
-        <v>71</v>
+        <v>155</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0302</v>
+        <v>0.3011</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0049</v>
+        <v>0.0485</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4559</v>
+        <v>-0.5021</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0302</v>
+        <v>0.3011</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.027</v>
+        <v>0.3011</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0032</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.027</v>
+        <v>0.3011</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0219</v>
+        <v>0.3011</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.0032</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="L29" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0251</v>
+        <v>0.3011</v>
       </c>
       <c r="N29" t="n">
-        <v>155</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1712</v>
+        <v>0.0173</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0276</v>
+        <v>0.0028</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5121</v>
+        <v>-0.6302</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1712</v>
+        <v>0.0173</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1712</v>
+        <v>0.0173</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1712</v>
+        <v>0.0173</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1712</v>
+        <v>0.0173</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1712</v>
+        <v>0.0173</v>
       </c>
       <c r="N30" t="n">
-        <v>71</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>AcilioN</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1748</v>
+        <v>-0.0136</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0282</v>
+        <v>-0.0022</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.6442</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1748</v>
+        <v>-0.0136</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.1312</v>
+        <v>-0.0136</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9564</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.1312</v>
+        <v>-0.0136</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.9169</v>
+        <v>-0.0136</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9564</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="L31" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.03949999999999998</v>
+        <v>-0.0136</v>
       </c>
       <c r="N31" t="n">
-        <v>155</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AcilioN</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3048</v>
+        <v>-0.0887</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0491</v>
+        <v>-0.0143</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5653</v>
+        <v>-0.6781</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3048</v>
+        <v>-0.0887</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3048</v>
+        <v>-0.0887</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3048</v>
+        <v>-0.0887</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3048</v>
+        <v>-0.0887</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3048</v>
+        <v>-0.0887</v>
       </c>
       <c r="N32" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.333</v>
+        <v>-0.1131</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0536</v>
+        <v>-0.0182</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5766</v>
+        <v>-0.6891</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.333</v>
+        <v>-0.1131</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.333</v>
+        <v>-0.1131</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.333</v>
+        <v>-0.1131</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.333</v>
+        <v>-0.1131</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.333</v>
+        <v>-0.1131</v>
       </c>
       <c r="N33" t="n">
-        <v>115</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3969</v>
+        <v>-0.2504</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0639</v>
+        <v>-0.0403</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.602</v>
+        <v>-0.7511</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3969</v>
+        <v>-0.2504</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3969</v>
+        <v>-0.2504</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3969</v>
+        <v>-0.2504</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3969</v>
+        <v>-0.2504</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3969</v>
+        <v>-0.2504</v>
       </c>
       <c r="N34" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4219</v>
+        <v>-0.252</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.068</v>
+        <v>-0.0406</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.612</v>
+        <v>-0.7518</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4219</v>
+        <v>-0.252</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4219</v>
+        <v>-0.252</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4219</v>
+        <v>-0.252</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4219</v>
+        <v>-0.252</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.4219</v>
+        <v>-0.252</v>
       </c>
       <c r="N35" t="n">
         <v>104</v>
@@ -2056,32 +2056,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.4421</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1217</v>
+        <v>-0.0712</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7449</v>
+        <v>-0.8376</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.4421</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.4421</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.4421</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.4421</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.4421</v>
       </c>
       <c r="N36" t="n">
         <v>108</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7764</v>
+        <v>-0.6456</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1251</v>
+        <v>-0.104</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.7532</v>
+        <v>-0.9295</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7764</v>
+        <v>-0.6456</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7764</v>
+        <v>-0.6456</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7764</v>
+        <v>-0.6456</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7764</v>
+        <v>-0.6456</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7764</v>
+        <v>-0.6456</v>
       </c>
       <c r="N37" t="n">
-        <v>108</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9196</v>
+        <v>-0.7671</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1481</v>
+        <v>-0.1236</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8103</v>
+        <v>-0.9843</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9196</v>
+        <v>-0.7671</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9196</v>
+        <v>-1.5269</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.7598</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9196</v>
+        <v>-1.5269</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9196</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.7598</v>
       </c>
       <c r="K38" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9196</v>
+        <v>-0.03410000000000002</v>
       </c>
       <c r="N38" t="n">
-        <v>71</v>
+        <v>155</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.4901</v>
+        <v>-0.8873</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2401</v>
+        <v>-0.1429</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0376</v>
+        <v>-1.0386</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4901</v>
+        <v>-0.8873</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4901</v>
+        <v>-0.8873</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4901</v>
+        <v>-0.8873</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.4901</v>
+        <v>-0.8873</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4901</v>
+        <v>-0.8873</v>
       </c>
       <c r="N39" t="n">
         <v>108</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9449</v>
+        <v>-1.3156</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3133</v>
+        <v>-0.2119</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2188</v>
+        <v>-1.2319</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9449</v>
+        <v>-1.3156</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.9449</v>
+        <v>-1.3156</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.9449</v>
+        <v>-1.3156</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.9449</v>
+        <v>-1.3156</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.9449</v>
+        <v>-1.3156</v>
       </c>
       <c r="N40" t="n">
         <v>71</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.5068</v>
+        <v>-3.8115</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5649</v>
+        <v>-0.614</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.841</v>
+        <v>-2.3587</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.5068</v>
+        <v>-3.8115</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.5068</v>
+        <v>-3.071</v>
       </c>
       <c r="G41" t="n">
-        <v>-1</v>
+        <v>-0.7405</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.5068</v>
+        <v>-3.071</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.0318</v>
+        <v>-1.5968</v>
       </c>
       <c r="J41" t="n">
-        <v>-1</v>
+        <v>-0.7405</v>
       </c>
       <c r="K41" t="n">
         <v>178</v>
@@ -2323,7 +2323,7 @@
         <v>53</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.0318</v>
+        <v>-2.3373</v>
       </c>
       <c r="N41" t="n">
         <v>231</v>
@@ -2429,10 +2429,10 @@
         <v>1.12</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3767</v>
+        <v>0.4212</v>
       </c>
       <c r="J2" t="n">
-        <v>8.2874</v>
+        <v>9.266400000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4449</v>
+        <v>-0.3079</v>
       </c>
       <c r="J3" t="n">
-        <v>-9.787800000000001</v>
+        <v>-6.7738</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.62</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.553</v>
+        <v>-0.3728</v>
       </c>
       <c r="J4" t="n">
-        <v>-12.166</v>
+        <v>-8.201599999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.62</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.553</v>
+        <v>-0.3728</v>
       </c>
       <c r="J5" t="n">
-        <v>-12.166</v>
+        <v>-8.201599999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.52</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6897</v>
+        <v>-0.4663</v>
       </c>
       <c r="J6" t="n">
-        <v>-15.1734</v>
+        <v>-10.2586</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.75</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6295</v>
+        <v>1.4143</v>
       </c>
       <c r="J7" t="n">
-        <v>35.849</v>
+        <v>31.1146</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.32</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7313</v>
+        <v>0.8112</v>
       </c>
       <c r="J8" t="n">
-        <v>16.0886</v>
+        <v>17.8464</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.32</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7313</v>
+        <v>0.8112</v>
       </c>
       <c r="J9" t="n">
-        <v>16.0886</v>
+        <v>17.8464</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.27</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6083</v>
+        <v>0.6994</v>
       </c>
       <c r="J10" t="n">
-        <v>13.3826</v>
+        <v>15.3868</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0026</v>
+        <v>0.0859</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0572</v>
+        <v>1.8898</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.23</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4077</v>
+        <v>0.4765</v>
       </c>
       <c r="J12" t="n">
-        <v>12.231</v>
+        <v>14.295</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.11</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2234</v>
+        <v>0.2544</v>
       </c>
       <c r="J13" t="n">
-        <v>6.702</v>
+        <v>7.632</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.08</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1688</v>
+        <v>0.1943</v>
       </c>
       <c r="J14" t="n">
-        <v>5.064</v>
+        <v>5.829</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.97</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1133</v>
+        <v>-0.0553</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.399</v>
+        <v>-1.659</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.88</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2758</v>
+        <v>-0.1622</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.273999999999999</v>
+        <v>-4.866</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.32</v>
       </c>
       <c r="I17" t="n">
-        <v>0.926</v>
+        <v>0.9006</v>
       </c>
       <c r="J17" t="n">
-        <v>27.78</v>
+        <v>27.018</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7883</v>
+        <v>0.7544</v>
       </c>
       <c r="J18" t="n">
-        <v>23.649</v>
+        <v>22.632</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3973</v>
+        <v>0.3637</v>
       </c>
       <c r="J19" t="n">
-        <v>11.919</v>
+        <v>10.911</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.84</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.5279</v>
       </c>
       <c r="J20" t="n">
-        <v>-17.466</v>
+        <v>-15.837</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.68</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.9346</v>
       </c>
       <c r="J21" t="n">
-        <v>-28.866</v>
+        <v>-28.038</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.01</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1276</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>3.0624</v>
+        <v>2.2848</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.9</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1231</v>
+        <v>-0.112</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.9544</v>
+        <v>-2.688</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.72</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4417</v>
+        <v>-0.2921</v>
       </c>
       <c r="J24" t="n">
-        <v>-10.6008</v>
+        <v>-7.0104</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.7</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4711</v>
+        <v>-0.3111</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.3064</v>
+        <v>-7.4664</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4856</v>
+        <v>-0.3206</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.6544</v>
+        <v>-7.6944</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.41</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9849</v>
+        <v>0.7331</v>
       </c>
       <c r="J27" t="n">
-        <v>23.6376</v>
+        <v>17.5944</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.35</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8491</v>
+        <v>0.6565</v>
       </c>
       <c r="J28" t="n">
-        <v>20.3784</v>
+        <v>15.756</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.33</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8006</v>
+        <v>0.6309</v>
       </c>
       <c r="J29" t="n">
-        <v>19.2144</v>
+        <v>15.1416</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.24</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5562</v>
+        <v>0.5129</v>
       </c>
       <c r="J30" t="n">
-        <v>13.3488</v>
+        <v>12.3096</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.17</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3803</v>
+        <v>0.4121</v>
       </c>
       <c r="J31" t="n">
-        <v>9.1272</v>
+        <v>9.8904</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.5</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7532</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>22.596</v>
+        <v>15.921</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1792</v>
+        <v>0.1411</v>
       </c>
       <c r="J33" t="n">
-        <v>5.376</v>
+        <v>4.233</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0969</v>
+        <v>0.079</v>
       </c>
       <c r="J34" t="n">
-        <v>2.907</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.79</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4048</v>
+        <v>-0.2527</v>
       </c>
       <c r="J35" t="n">
-        <v>-12.144</v>
+        <v>-7.581</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.75</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4599</v>
+        <v>-0.2919</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.797</v>
+        <v>-8.757</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5707</v>
+        <v>0.4485</v>
       </c>
       <c r="J37" t="n">
-        <v>17.121</v>
+        <v>13.455</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.15</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2793</v>
+        <v>0.2491</v>
       </c>
       <c r="J38" t="n">
-        <v>8.379</v>
+        <v>7.473</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1067</v>
+        <v>0.1147</v>
       </c>
       <c r="J39" t="n">
-        <v>3.201</v>
+        <v>3.441</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1804</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.412</v>
+        <v>-2.898</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.89</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2659</v>
+        <v>-0.1541</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.977</v>
+        <v>-4.623</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.09</v>
       </c>
       <c r="I42" t="n">
-        <v>0.284</v>
+        <v>0.2938</v>
       </c>
       <c r="J42" t="n">
-        <v>6.248</v>
+        <v>6.4636</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.86</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1973</v>
+        <v>-0.1572</v>
       </c>
       <c r="J43" t="n">
-        <v>-4.3406</v>
+        <v>-3.4584</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.77</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3673</v>
+        <v>-0.2452</v>
       </c>
       <c r="J44" t="n">
-        <v>-8.0806</v>
+        <v>-5.3944</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.74</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4146</v>
+        <v>-0.274</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.1212</v>
+        <v>-6.028</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.6</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6107</v>
+        <v>-0.4064</v>
       </c>
       <c r="J46" t="n">
-        <v>-13.4354</v>
+        <v>-8.940799999999999</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.53</v>
       </c>
       <c r="I47" t="n">
-        <v>1.228</v>
+        <v>0.8812</v>
       </c>
       <c r="J47" t="n">
-        <v>27.016</v>
+        <v>19.3864</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.48</v>
       </c>
       <c r="I48" t="n">
-        <v>1.1268</v>
+        <v>0.8192</v>
       </c>
       <c r="J48" t="n">
-        <v>24.7896</v>
+        <v>18.0224</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.39</v>
       </c>
       <c r="I49" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.706</v>
       </c>
       <c r="J49" t="n">
-        <v>20.548</v>
+        <v>15.532</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.2</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4507</v>
+        <v>0.4548</v>
       </c>
       <c r="J50" t="n">
-        <v>9.9154</v>
+        <v>10.0056</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.96</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3287</v>
+        <v>-0.2438</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.2314</v>
+        <v>-5.3636</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.38</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9998</v>
+        <v>0.723</v>
       </c>
       <c r="J52" t="n">
-        <v>29.994</v>
+        <v>21.69</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.24</v>
       </c>
       <c r="I53" t="n">
-        <v>0.678</v>
+        <v>0.5302</v>
       </c>
       <c r="J53" t="n">
-        <v>20.34</v>
+        <v>15.906</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.15</v>
       </c>
       <c r="I54" t="n">
-        <v>0.428</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
-        <v>12.84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1025</v>
+        <v>-0.0353</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.075</v>
+        <v>-1.059</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.97</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2417</v>
+        <v>-0.1686</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.251</v>
+        <v>-5.058</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.31</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5393</v>
+        <v>0.5153</v>
       </c>
       <c r="J57" t="n">
-        <v>16.179</v>
+        <v>15.459</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.26</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4734</v>
+        <v>0.4634</v>
       </c>
       <c r="J58" t="n">
-        <v>14.202</v>
+        <v>13.902</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.86</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2883</v>
+        <v>-0.1754</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.648999999999999</v>
+        <v>-5.262</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.86</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2883</v>
+        <v>-0.1754</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.648999999999999</v>
+        <v>-5.262</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.62</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6186</v>
+        <v>-0.409</v>
       </c>
       <c r="J61" t="n">
-        <v>-18.558</v>
+        <v>-12.27</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.71</v>
       </c>
       <c r="I62" t="n">
-        <v>1.5823</v>
+        <v>1.1069</v>
       </c>
       <c r="J62" t="n">
-        <v>36.3929</v>
+        <v>25.4587</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.51</v>
       </c>
       <c r="I63" t="n">
-        <v>1.2014</v>
+        <v>0.8618</v>
       </c>
       <c r="J63" t="n">
-        <v>27.6322</v>
+        <v>19.8214</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.43</v>
       </c>
       <c r="I64" t="n">
-        <v>1.0363</v>
+        <v>0.7611</v>
       </c>
       <c r="J64" t="n">
-        <v>23.8349</v>
+        <v>17.5053</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.24</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5656</v>
+        <v>0.5147</v>
       </c>
       <c r="J65" t="n">
-        <v>13.0088</v>
+        <v>11.8381</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.53</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.3137</v>
+        <v>-1.3361</v>
       </c>
       <c r="J66" t="n">
-        <v>-30.2151</v>
+        <v>-30.7303</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.13</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3485</v>
+        <v>0.3606</v>
       </c>
       <c r="J67" t="n">
-        <v>8.015499999999999</v>
+        <v>8.293799999999999</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.92</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0916</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.1068</v>
+        <v>-2.0792</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.78</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3517</v>
+        <v>-0.2359</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.0891</v>
+        <v>-5.4257</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.68</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.503</v>
+        <v>-0.3315</v>
       </c>
       <c r="J70" t="n">
-        <v>-11.569</v>
+        <v>-7.6245</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6626</v>
+        <v>-0.4439</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.2398</v>
+        <v>-10.2097</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.41</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7019</v>
+        <v>0.87</v>
       </c>
       <c r="J72" t="n">
-        <v>18.9513</v>
+        <v>23.49</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.09</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2576</v>
+        <v>0.2643</v>
       </c>
       <c r="J73" t="n">
-        <v>6.9552</v>
+        <v>7.1361</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.74</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.4376</v>
+        <v>-0.2829</v>
       </c>
       <c r="J74" t="n">
-        <v>-11.8152</v>
+        <v>-7.6383</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.65</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5608</v>
+        <v>-0.3686</v>
       </c>
       <c r="J75" t="n">
-        <v>-15.1416</v>
+        <v>-9.952199999999999</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.5</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7478</v>
+        <v>-0.507</v>
       </c>
       <c r="J76" t="n">
-        <v>-20.1906</v>
+        <v>-13.689</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.4</v>
       </c>
       <c r="I77" t="n">
-        <v>1.001</v>
+        <v>0.9981</v>
       </c>
       <c r="J77" t="n">
-        <v>27.027</v>
+        <v>26.9487</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.34</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8685</v>
+        <v>0.8767</v>
       </c>
       <c r="J78" t="n">
-        <v>23.4495</v>
+        <v>23.6709</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.32</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8224</v>
+        <v>0.8316</v>
       </c>
       <c r="J79" t="n">
-        <v>22.2048</v>
+        <v>22.4532</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.21</v>
       </c>
       <c r="I80" t="n">
-        <v>0.5253</v>
+        <v>0.5799</v>
       </c>
       <c r="J80" t="n">
-        <v>14.1831</v>
+        <v>15.6573</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.87</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5641</v>
+        <v>-0.4952</v>
       </c>
       <c r="J81" t="n">
-        <v>-15.2307</v>
+        <v>-13.3704</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.33</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6217</v>
+        <v>0.7581</v>
       </c>
       <c r="J82" t="n">
-        <v>15.5425</v>
+        <v>18.9525</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.06</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2234</v>
+        <v>0.2166</v>
       </c>
       <c r="J83" t="n">
-        <v>5.585</v>
+        <v>5.415</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.76</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3912</v>
+        <v>-0.2572</v>
       </c>
       <c r="J84" t="n">
-        <v>-9.779999999999999</v>
+        <v>-6.43</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.55</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.6785</v>
+        <v>-0.4553</v>
       </c>
       <c r="J85" t="n">
-        <v>-16.9625</v>
+        <v>-11.3825</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.45</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7998</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>-19.995</v>
+        <v>-13.6725</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.7</v>
       </c>
       <c r="I87" t="n">
-        <v>1.5586</v>
+        <v>1.3656</v>
       </c>
       <c r="J87" t="n">
-        <v>38.965</v>
+        <v>34.14</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.28</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6614</v>
+        <v>0.7298</v>
       </c>
       <c r="J88" t="n">
-        <v>16.535</v>
+        <v>18.245</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.26</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6091</v>
+        <v>0.6847</v>
       </c>
       <c r="J89" t="n">
-        <v>15.2275</v>
+        <v>17.1175</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.13</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2777</v>
+        <v>0.3628</v>
       </c>
       <c r="J90" t="n">
-        <v>6.9425</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.11</v>
       </c>
       <c r="I91" t="n">
-        <v>0.2237</v>
+        <v>0.3081</v>
       </c>
       <c r="J91" t="n">
-        <v>5.5925</v>
+        <v>7.7025</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.37</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5524</v>
+        <v>0.4826</v>
       </c>
       <c r="J92" t="n">
-        <v>12.7052</v>
+        <v>11.0998</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.31</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4751</v>
+        <v>0.4136</v>
       </c>
       <c r="J93" t="n">
-        <v>10.9273</v>
+        <v>9.5128</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.23</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3632</v>
+        <v>0.3192</v>
       </c>
       <c r="J94" t="n">
-        <v>8.3536</v>
+        <v>7.3416</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.05</v>
       </c>
       <c r="I95" t="n">
-        <v>0.053</v>
+        <v>0.0791</v>
       </c>
       <c r="J95" t="n">
-        <v>1.219</v>
+        <v>1.8193</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2031</v>
+        <v>-0.1068</v>
       </c>
       <c r="J96" t="n">
-        <v>-4.6713</v>
+        <v>-2.4564</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.26</v>
       </c>
       <c r="I97" t="n">
-        <v>0.481</v>
+        <v>0.4302</v>
       </c>
       <c r="J97" t="n">
-        <v>11.063</v>
+        <v>9.894600000000001</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3235</v>
+        <v>0.2734</v>
       </c>
       <c r="J98" t="n">
-        <v>7.4405</v>
+        <v>6.2882</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.84</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3132</v>
+        <v>-0.1936</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.2036</v>
+        <v>-4.4528</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.83</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3287</v>
+        <v>-0.2039</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.5601</v>
+        <v>-4.6897</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.72</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4859</v>
+        <v>-0.3125</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.1757</v>
+        <v>-7.1875</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.26</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4975</v>
+        <v>0.5823</v>
       </c>
       <c r="J102" t="n">
-        <v>12.4375</v>
+        <v>14.5575</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.93</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1223</v>
+        <v>-0.0925</v>
       </c>
       <c r="J103" t="n">
-        <v>-3.0575</v>
+        <v>-2.3125</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.9</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1915</v>
+        <v>-0.1253</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.7875</v>
+        <v>-3.1325</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.77</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4048</v>
+        <v>-0.2583</v>
       </c>
       <c r="J105" t="n">
-        <v>-10.12</v>
+        <v>-6.4575</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.71</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.489</v>
+        <v>-0.3164</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.225</v>
+        <v>-7.91</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.77</v>
       </c>
       <c r="I107" t="n">
-        <v>1.7375</v>
+        <v>1.484</v>
       </c>
       <c r="J107" t="n">
-        <v>43.4375</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.58</v>
       </c>
       <c r="I108" t="n">
-        <v>1.3869</v>
+        <v>1.2475</v>
       </c>
       <c r="J108" t="n">
-        <v>34.6725</v>
+        <v>31.1875</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.11</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2736</v>
+        <v>0.3341</v>
       </c>
       <c r="J109" t="n">
-        <v>6.84</v>
+        <v>8.352499999999999</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.78</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.7729</v>
+        <v>-0.7225</v>
       </c>
       <c r="J110" t="n">
-        <v>-19.3225</v>
+        <v>-18.0625</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.68</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.9951</v>
+        <v>-0.9693000000000001</v>
       </c>
       <c r="J111" t="n">
-        <v>-24.8775</v>
+        <v>-24.2325</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.8</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.1939</v>
+        <v>-0.1763</v>
       </c>
       <c r="J112" t="n">
-        <v>-3.878</v>
+        <v>-3.526</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.75</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2718</v>
+        <v>-0.2307</v>
       </c>
       <c r="J113" t="n">
-        <v>-5.436</v>
+        <v>-4.614</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.64</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4469</v>
+        <v>-0.3404</v>
       </c>
       <c r="J114" t="n">
-        <v>-8.938000000000001</v>
+        <v>-6.808</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.46</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.7393</v>
+        <v>-0.5054</v>
       </c>
       <c r="J115" t="n">
-        <v>-14.786</v>
+        <v>-10.108</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.42</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7924</v>
+        <v>-0.5434</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.848</v>
+        <v>-10.868</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.86</v>
       </c>
       <c r="I117" t="n">
-        <v>1.7622</v>
+        <v>1.5095</v>
       </c>
       <c r="J117" t="n">
-        <v>35.244</v>
+        <v>30.19</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.52</v>
       </c>
       <c r="I118" t="n">
-        <v>1.1187</v>
+        <v>1.1181</v>
       </c>
       <c r="J118" t="n">
-        <v>22.374</v>
+        <v>22.362</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.51</v>
       </c>
       <c r="I119" t="n">
-        <v>1.0962</v>
+        <v>1.1065</v>
       </c>
       <c r="J119" t="n">
-        <v>21.924</v>
+        <v>22.13</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.48</v>
       </c>
       <c r="I120" t="n">
-        <v>1.0163</v>
+        <v>1.072</v>
       </c>
       <c r="J120" t="n">
-        <v>20.326</v>
+        <v>21.44</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.06</v>
       </c>
       <c r="I121" t="n">
-        <v>0.0289</v>
+        <v>0.12</v>
       </c>
       <c r="J121" t="n">
-        <v>0.578</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.52</v>
       </c>
       <c r="I122" t="n">
-        <v>1.2952</v>
+        <v>1.1852</v>
       </c>
       <c r="J122" t="n">
-        <v>33.6752</v>
+        <v>30.8152</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.31</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.8378</v>
       </c>
       <c r="J123" t="n">
-        <v>22.1598</v>
+        <v>21.7828</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.08</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2125</v>
+        <v>0.2603</v>
       </c>
       <c r="J124" t="n">
-        <v>5.525</v>
+        <v>6.7678</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.93</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3675</v>
+        <v>-0.2968</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.555</v>
+        <v>-7.7168</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.83</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6392</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="J126" t="n">
-        <v>-16.6192</v>
+        <v>-15.0826</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.54</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7967</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="J127" t="n">
-        <v>20.7142</v>
+        <v>25.7244</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.06</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1374</v>
+        <v>0.1548</v>
       </c>
       <c r="J128" t="n">
-        <v>3.5724</v>
+        <v>4.0248</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.05</v>
       </c>
       <c r="I129" t="n">
-        <v>0.116</v>
+        <v>0.1328</v>
       </c>
       <c r="J129" t="n">
-        <v>3.016</v>
+        <v>3.4528</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.86</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3032</v>
+        <v>-0.1818</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.8832</v>
+        <v>-4.7268</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5524</v>
+        <v>-0.3592</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.3624</v>
+        <v>-9.3392</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.46</v>
       </c>
       <c r="I132" t="n">
-        <v>1.1242</v>
+        <v>1.0825</v>
       </c>
       <c r="J132" t="n">
-        <v>26.9808</v>
+        <v>25.98</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.34</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8651</v>
+        <v>0.8751</v>
       </c>
       <c r="J133" t="n">
-        <v>20.7624</v>
+        <v>21.0024</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.22</v>
       </c>
       <c r="I134" t="n">
-        <v>0.5486</v>
+        <v>0.6025</v>
       </c>
       <c r="J134" t="n">
-        <v>13.1664</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.22</v>
       </c>
       <c r="I135" t="n">
-        <v>0.5486</v>
+        <v>0.6025</v>
       </c>
       <c r="J135" t="n">
-        <v>13.1664</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.93</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4006</v>
+        <v>-0.3223</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.6144</v>
+        <v>-7.7352</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.23</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4864</v>
+        <v>0.5669</v>
       </c>
       <c r="J137" t="n">
-        <v>11.6736</v>
+        <v>13.6056</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.99</v>
       </c>
       <c r="I138" t="n">
-        <v>0.0451</v>
+        <v>0.0022</v>
       </c>
       <c r="J138" t="n">
-        <v>1.0824</v>
+        <v>0.0528</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.74</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.4238</v>
+        <v>-0.2773</v>
       </c>
       <c r="J139" t="n">
-        <v>-10.1712</v>
+        <v>-6.6552</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.72</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4532</v>
+        <v>-0.2965</v>
       </c>
       <c r="J140" t="n">
-        <v>-10.8768</v>
+        <v>-7.116</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.5</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.7411</v>
+        <v>-0.502</v>
       </c>
       <c r="J141" t="n">
-        <v>-17.7864</v>
+        <v>-12.048</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.2</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6202</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="J142" t="n">
-        <v>25.4282</v>
+        <v>24.1982</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.18</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5684</v>
+        <v>0.5393</v>
       </c>
       <c r="J143" t="n">
-        <v>23.3044</v>
+        <v>22.1113</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.15</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4873</v>
+        <v>0.4614</v>
       </c>
       <c r="J144" t="n">
-        <v>19.9793</v>
+        <v>18.9174</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.13</v>
       </c>
       <c r="I145" t="n">
-        <v>0.4303</v>
+        <v>0.4083</v>
       </c>
       <c r="J145" t="n">
-        <v>17.6423</v>
+        <v>16.7403</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.8602</v>
+        <v>-0.8214</v>
       </c>
       <c r="J146" t="n">
-        <v>-35.2682</v>
+        <v>-33.6774</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.28</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4688</v>
+        <v>0.5571</v>
       </c>
       <c r="J147" t="n">
-        <v>19.2208</v>
+        <v>22.8411</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.12</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2312</v>
+        <v>0.2697</v>
       </c>
       <c r="J148" t="n">
-        <v>9.479200000000001</v>
+        <v>11.0577</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.03</v>
       </c>
       <c r="I149" t="n">
-        <v>0.045</v>
+        <v>0.0814</v>
       </c>
       <c r="J149" t="n">
-        <v>1.845</v>
+        <v>3.3374</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.99</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.0728</v>
+        <v>-0.0275</v>
       </c>
       <c r="J150" t="n">
-        <v>-2.9848</v>
+        <v>-1.1275</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.96</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.1409</v>
+        <v>-0.0709</v>
       </c>
       <c r="J151" t="n">
-        <v>-5.7769</v>
+        <v>-2.9069</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.82</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.1709</v>
+        <v>-0.1592</v>
       </c>
       <c r="J152" t="n">
-        <v>-3.418</v>
+        <v>-3.184</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.67</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.4076</v>
+        <v>-0.3152</v>
       </c>
       <c r="J153" t="n">
-        <v>-8.151999999999999</v>
+        <v>-6.304</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.64</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4603</v>
+        <v>-0.3428</v>
       </c>
       <c r="J154" t="n">
-        <v>-9.206</v>
+        <v>-6.856</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.52</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.6623</v>
+        <v>-0.4518</v>
       </c>
       <c r="J155" t="n">
-        <v>-13.246</v>
+        <v>-9.036</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.5</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6902</v>
+        <v>-0.4706</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.804</v>
+        <v>-9.412000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.84</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9782</v>
+        <v>0.9083</v>
       </c>
       <c r="J157" t="n">
-        <v>19.564</v>
+        <v>18.166</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.73</v>
       </c>
       <c r="I158" t="n">
-        <v>0.8647</v>
+        <v>0.8032</v>
       </c>
       <c r="J158" t="n">
-        <v>17.294</v>
+        <v>16.064</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.47</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5492</v>
+        <v>0.5495</v>
       </c>
       <c r="J159" t="n">
-        <v>10.984</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.41</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4769</v>
+        <v>0.4867</v>
       </c>
       <c r="J160" t="n">
-        <v>9.538</v>
+        <v>9.734</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.3</v>
       </c>
       <c r="I161" t="n">
-        <v>0.3429</v>
+        <v>0.3652</v>
       </c>
       <c r="J161" t="n">
-        <v>6.858</v>
+        <v>7.304</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.36</v>
       </c>
       <c r="I162" t="n">
-        <v>0.9649</v>
+        <v>0.9516</v>
       </c>
       <c r="J162" t="n">
-        <v>27.0172</v>
+        <v>26.6448</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.3</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8304</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="J163" t="n">
-        <v>23.2512</v>
+        <v>22.82</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.11</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3082</v>
+        <v>0.3451</v>
       </c>
       <c r="J164" t="n">
-        <v>8.6296</v>
+        <v>9.662800000000001</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2704</v>
+        <v>-0.1994</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.5712</v>
+        <v>-5.5832</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.93</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3668</v>
+        <v>-0.2963</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.2704</v>
+        <v>-8.2964</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.03</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1339</v>
+        <v>0.1152</v>
       </c>
       <c r="J167" t="n">
-        <v>3.7492</v>
+        <v>3.2256</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.02</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1113</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="J168" t="n">
-        <v>3.1164</v>
+        <v>2.4752</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.85</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2772</v>
+        <v>-0.1768</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.7616</v>
+        <v>-4.9504</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.82</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3261</v>
+        <v>-0.2073</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.130800000000001</v>
+        <v>-5.8044</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3571</v>
+        <v>-0.2274</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.998799999999999</v>
+        <v>-6.3672</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.46</v>
       </c>
       <c r="I172" t="n">
-        <v>0.7403999999999999</v>
+        <v>0.9213</v>
       </c>
       <c r="J172" t="n">
-        <v>21.4716</v>
+        <v>26.7177</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.09</v>
       </c>
       <c r="I173" t="n">
-        <v>0.236</v>
+        <v>0.2443</v>
       </c>
       <c r="J173" t="n">
-        <v>6.844</v>
+        <v>7.0847</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3514</v>
+        <v>-0.2211</v>
       </c>
       <c r="J174" t="n">
-        <v>-10.1906</v>
+        <v>-6.4119</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.66</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5597</v>
+        <v>-0.3663</v>
       </c>
       <c r="J175" t="n">
-        <v>-16.2313</v>
+        <v>-10.6227</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.65</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5725</v>
+        <v>-0.3756</v>
       </c>
       <c r="J176" t="n">
-        <v>-16.6025</v>
+        <v>-10.8924</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.39</v>
       </c>
       <c r="I177" t="n">
-        <v>1.017</v>
+        <v>1.0007</v>
       </c>
       <c r="J177" t="n">
-        <v>29.493</v>
+        <v>29.0203</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.33</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8855</v>
+        <v>0.8766</v>
       </c>
       <c r="J178" t="n">
-        <v>25.6795</v>
+        <v>25.4214</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.18</v>
       </c>
       <c r="I179" t="n">
-        <v>0.5139</v>
+        <v>0.5189</v>
       </c>
       <c r="J179" t="n">
-        <v>14.9031</v>
+        <v>15.0481</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.17</v>
       </c>
       <c r="I180" t="n">
-        <v>0.4844</v>
+        <v>0.4942</v>
       </c>
       <c r="J180" t="n">
-        <v>14.0476</v>
+        <v>14.3318</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.71</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.9243</v>
+        <v>-0.8902</v>
       </c>
       <c r="J181" t="n">
-        <v>-26.8047</v>
+        <v>-25.8158</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.85</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.0843</v>
+        <v>-0.0961</v>
       </c>
       <c r="J182" t="n">
-        <v>-1.6017</v>
+        <v>-1.8259</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.72</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2878</v>
+        <v>-0.2458</v>
       </c>
       <c r="J183" t="n">
-        <v>-5.4682</v>
+        <v>-4.6702</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.53</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.4298</v>
       </c>
       <c r="J184" t="n">
-        <v>-11.6356</v>
+        <v>-8.1662</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.39</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.8164</v>
+        <v>-0.5623</v>
       </c>
       <c r="J185" t="n">
-        <v>-15.5116</v>
+        <v>-10.6837</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.32</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.6304</v>
       </c>
       <c r="J186" t="n">
-        <v>-17.2482</v>
+        <v>-11.9776</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.78</v>
       </c>
       <c r="I187" t="n">
-        <v>1.6111</v>
+        <v>1.4142</v>
       </c>
       <c r="J187" t="n">
-        <v>30.6109</v>
+        <v>26.8698</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.58</v>
       </c>
       <c r="I188" t="n">
-        <v>1.2314</v>
+        <v>1.1852</v>
       </c>
       <c r="J188" t="n">
-        <v>23.3966</v>
+        <v>22.5188</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.48</v>
       </c>
       <c r="I189" t="n">
-        <v>0.9969</v>
+        <v>1.0701</v>
       </c>
       <c r="J189" t="n">
-        <v>18.9411</v>
+        <v>20.3319</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.41</v>
       </c>
       <c r="I190" t="n">
-        <v>0.8448</v>
+        <v>0.969</v>
       </c>
       <c r="J190" t="n">
-        <v>16.0512</v>
+        <v>18.411</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.31</v>
       </c>
       <c r="I191" t="n">
-        <v>0.6299</v>
+        <v>0.7564</v>
       </c>
       <c r="J191" t="n">
-        <v>11.9681</v>
+        <v>14.3716</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.82</v>
       </c>
       <c r="I192" t="n">
-        <v>1.7087</v>
+        <v>1.4721</v>
       </c>
       <c r="J192" t="n">
-        <v>35.8827</v>
+        <v>30.9141</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.78</v>
       </c>
       <c r="I193" t="n">
-        <v>1.6381</v>
+        <v>1.4263</v>
       </c>
       <c r="J193" t="n">
-        <v>34.4001</v>
+        <v>29.9523</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.67</v>
       </c>
       <c r="I194" t="n">
-        <v>1.4374</v>
+        <v>1.2989</v>
       </c>
       <c r="J194" t="n">
-        <v>30.1854</v>
+        <v>27.2769</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.05</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0074</v>
+        <v>0.0963</v>
       </c>
       <c r="J195" t="n">
-        <v>0.1554</v>
+        <v>2.0223</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.91</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5063</v>
+        <v>-0.4283</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.6323</v>
+        <v>-8.994300000000001</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.98</v>
       </c>
       <c r="I197" t="n">
-        <v>0.0804</v>
+        <v>0.0382</v>
       </c>
       <c r="J197" t="n">
-        <v>1.6884</v>
+        <v>0.8022</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.89</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.0916</v>
+        <v>-0.0998</v>
       </c>
       <c r="J198" t="n">
-        <v>-1.9236</v>
+        <v>-2.0958</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.73</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3537</v>
+        <v>-0.2701</v>
       </c>
       <c r="J199" t="n">
-        <v>-7.4277</v>
+        <v>-5.6721</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.59</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5904</v>
+        <v>-0.3986</v>
       </c>
       <c r="J200" t="n">
-        <v>-12.3984</v>
+        <v>-8.3706</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.31</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.9449</v>
+        <v>-0.6599</v>
       </c>
       <c r="J201" t="n">
-        <v>-19.8429</v>
+        <v>-13.8579</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.07</v>
       </c>
       <c r="I202" t="n">
-        <v>0.2162</v>
+        <v>0.2141</v>
       </c>
       <c r="J202" t="n">
-        <v>5.6212</v>
+        <v>5.5666</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0555</v>
+        <v>0.0225</v>
       </c>
       <c r="J203" t="n">
-        <v>1.443</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.85</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2728</v>
+        <v>-0.1757</v>
       </c>
       <c r="J204" t="n">
-        <v>-7.0928</v>
+        <v>-4.5682</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.85</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2728</v>
+        <v>-0.1757</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.0928</v>
+        <v>-4.5682</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.7</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4978</v>
+        <v>-0.3234</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.9428</v>
+        <v>-8.4084</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.91</v>
       </c>
       <c r="I207" t="n">
-        <v>1.9052</v>
+        <v>1.6056</v>
       </c>
       <c r="J207" t="n">
-        <v>49.5352</v>
+        <v>41.7456</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.47</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0992</v>
+        <v>1.0782</v>
       </c>
       <c r="J208" t="n">
-        <v>28.5792</v>
+        <v>28.0332</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.27</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6159</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="J209" t="n">
-        <v>16.0134</v>
+        <v>18.2546</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.05</v>
       </c>
       <c r="I210" t="n">
-        <v>0.039</v>
+        <v>0.1223</v>
       </c>
       <c r="J210" t="n">
-        <v>1.014</v>
+        <v>3.1798</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.93</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4248</v>
+        <v>-0.3437</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.0448</v>
+        <v>-8.936199999999999</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.2109</v>
+        <v>-0.1838</v>
       </c>
       <c r="J212" t="n">
-        <v>-4.8507</v>
+        <v>-4.2274</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.75</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.3064</v>
+        <v>-0.2462</v>
       </c>
       <c r="J213" t="n">
-        <v>-7.0472</v>
+        <v>-5.6626</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.75</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3064</v>
+        <v>-0.2462</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.0472</v>
+        <v>-5.6626</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.61</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.5513</v>
+        <v>-0.376</v>
       </c>
       <c r="J215" t="n">
-        <v>-12.6799</v>
+        <v>-8.648</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.46</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.7573</v>
+        <v>-0.5163</v>
       </c>
       <c r="J216" t="n">
-        <v>-17.4179</v>
+        <v>-11.8749</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.51</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1378</v>
+        <v>1.1143</v>
       </c>
       <c r="J217" t="n">
-        <v>26.1694</v>
+        <v>25.6289</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.49</v>
       </c>
       <c r="I218" t="n">
-        <v>1.0956</v>
+        <v>1.0903</v>
       </c>
       <c r="J218" t="n">
-        <v>25.1988</v>
+        <v>25.0769</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.48</v>
       </c>
       <c r="I219" t="n">
-        <v>1.0742</v>
+        <v>1.0782</v>
       </c>
       <c r="J219" t="n">
-        <v>24.7066</v>
+        <v>24.7986</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.37</v>
       </c>
       <c r="I220" t="n">
-        <v>0.804</v>
+        <v>0.9066</v>
       </c>
       <c r="J220" t="n">
-        <v>18.492</v>
+        <v>20.8518</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.22</v>
       </c>
       <c r="I221" t="n">
-        <v>0.4592</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="J221" t="n">
-        <v>10.5616</v>
+        <v>13.018</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.8</v>
       </c>
       <c r="I222" t="n">
-        <v>1.7542</v>
+        <v>1.4956</v>
       </c>
       <c r="J222" t="n">
-        <v>36.8382</v>
+        <v>31.4076</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.48</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1523</v>
+        <v>1.1026</v>
       </c>
       <c r="J223" t="n">
-        <v>24.1983</v>
+        <v>23.1546</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.03</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.007</v>
+        <v>0.0698</v>
       </c>
       <c r="J224" t="n">
-        <v>-0.147</v>
+        <v>1.4658</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1438</v>
+        <v>-0.0634</v>
       </c>
       <c r="J225" t="n">
-        <v>-3.0198</v>
+        <v>-1.3314</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.99</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2018</v>
+        <v>-0.1183</v>
       </c>
       <c r="J226" t="n">
-        <v>-4.2378</v>
+        <v>-2.4843</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.1</v>
       </c>
       <c r="I227" t="n">
-        <v>0.269</v>
+        <v>0.2803</v>
       </c>
       <c r="J227" t="n">
-        <v>5.649</v>
+        <v>5.8863</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1</v>
       </c>
       <c r="I228" t="n">
-        <v>0.0563</v>
+        <v>0.0231</v>
       </c>
       <c r="J228" t="n">
-        <v>1.1823</v>
+        <v>0.4851</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.87</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2362</v>
+        <v>-0.1549</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.9602</v>
+        <v>-3.2529</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.76</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4129</v>
+        <v>-0.2653</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.6709</v>
+        <v>-5.5713</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.73</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4558</v>
+        <v>-0.2944</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.5718</v>
+        <v>-6.1824</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2568/event_2568_evp_summary.xlsx
+++ b/database/event/2568/event_2568_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.376</v>
+        <v>6.52</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0272</v>
+        <v>1.0504</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2404</v>
+        <v>2.3438</v>
       </c>
       <c r="E2" t="n">
-        <v>6.376</v>
+        <v>6.52</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3321</v>
+        <v>2.2349</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0439</v>
+        <v>4.2851</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7304</v>
+        <v>2.4797</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4197</v>
+        <v>1.339</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0439</v>
+        <v>4.2851</v>
       </c>
       <c r="K2" t="n">
         <v>125</v>
@@ -529,7 +529,7 @@
         <v>128</v>
       </c>
       <c r="M2" t="n">
-        <v>5.4636</v>
+        <v>5.6241</v>
       </c>
       <c r="N2" t="n">
         <v>253</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4469</v>
+        <v>5.4447</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.8771</v>
       </c>
       <c r="D3" t="n">
-        <v>1.821</v>
+        <v>1.8543</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4469</v>
+        <v>5.4447</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0684</v>
+        <v>2.9453</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3785</v>
+        <v>2.4994</v>
       </c>
       <c r="H3" t="n">
-        <v>5.3247</v>
+        <v>4.8236</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7686</v>
+        <v>2.6047</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3785</v>
+        <v>2.4994</v>
       </c>
       <c r="K3" t="n">
         <v>125</v>
@@ -575,7 +575,7 @@
         <v>128</v>
       </c>
       <c r="M3" t="n">
-        <v>5.1471</v>
+        <v>5.1041</v>
       </c>
       <c r="N3" t="n">
         <v>253</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.7382</v>
+        <v>4.702</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7633</v>
+        <v>0.7575</v>
       </c>
       <c r="D4" t="n">
-        <v>1.501</v>
+        <v>1.5162</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7382</v>
+        <v>4.702</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9142</v>
+        <v>3.8266</v>
       </c>
       <c r="G4" t="n">
-        <v>0.824</v>
+        <v>0.8754</v>
       </c>
       <c r="H4" t="n">
-        <v>8.3048</v>
+        <v>7.731</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3181</v>
+        <v>4.1747</v>
       </c>
       <c r="J4" t="n">
-        <v>0.824</v>
+        <v>0.8754</v>
       </c>
       <c r="K4" t="n">
         <v>178</v>
@@ -621,7 +621,7 @@
         <v>53</v>
       </c>
       <c r="M4" t="n">
-        <v>5.1421</v>
+        <v>5.0501</v>
       </c>
       <c r="N4" t="n">
         <v>231</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5567</v>
+        <v>4.6007</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7341</v>
+        <v>0.7412</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4191</v>
+        <v>1.4701</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5567</v>
+        <v>4.6007</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8136</v>
+        <v>2.741</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7431</v>
+        <v>1.8597</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4271</v>
+        <v>4.1493</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3019</v>
+        <v>2.2406</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7431</v>
+        <v>1.8597</v>
       </c>
       <c r="K5" t="n">
         <v>50</v>
@@ -667,7 +667,7 @@
         <v>105</v>
       </c>
       <c r="M5" t="n">
-        <v>4.045</v>
+        <v>4.1003</v>
       </c>
       <c r="N5" t="n">
         <v>155</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4018</v>
+        <v>4.5214</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7091</v>
+        <v>0.7284</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3492</v>
+        <v>1.434</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4018</v>
+        <v>4.5214</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9136</v>
+        <v>2.8296</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4882</v>
+        <v>1.6918</v>
       </c>
       <c r="H6" t="n">
-        <v>4.7793</v>
+        <v>4.4417</v>
       </c>
       <c r="I6" t="n">
-        <v>2.485</v>
+        <v>2.3985</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4882</v>
+        <v>1.6918</v>
       </c>
       <c r="K6" t="n">
         <v>125</v>
@@ -713,7 +713,7 @@
         <v>128</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9732</v>
+        <v>4.0903</v>
       </c>
       <c r="N6" t="n">
         <v>253</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3081</v>
+        <v>4.3541</v>
       </c>
       <c r="C7" t="n">
-        <v>0.694</v>
+        <v>0.7014</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3069</v>
+        <v>1.3579</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3081</v>
+        <v>4.3541</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8124</v>
+        <v>2.7314</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4957</v>
+        <v>1.6227</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4227</v>
+        <v>4.1177</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2996</v>
+        <v>2.2235</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4957</v>
+        <v>1.6227</v>
       </c>
       <c r="K7" t="n">
         <v>50</v>
@@ -759,7 +759,7 @@
         <v>105</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7953</v>
+        <v>3.8462</v>
       </c>
       <c r="N7" t="n">
         <v>155</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2971</v>
+        <v>3.2502</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5312</v>
+        <v>0.5236</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8505</v>
+        <v>0.8554</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2971</v>
+        <v>3.2502</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8291</v>
+        <v>2.7928</v>
       </c>
       <c r="G8" t="n">
-        <v>0.468</v>
+        <v>0.4574</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4817</v>
+        <v>4.3204</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3303</v>
+        <v>2.333</v>
       </c>
       <c r="J8" t="n">
-        <v>0.468</v>
+        <v>0.4574</v>
       </c>
       <c r="K8" t="n">
         <v>45</v>
@@ -805,7 +805,7 @@
         <v>76</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7983</v>
+        <v>2.7904</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.7649</v>
+        <v>2.742</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4454</v>
+        <v>0.4417</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6102</v>
+        <v>0.624</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7649</v>
+        <v>2.742</v>
       </c>
       <c r="F9" t="n">
-        <v>2.712</v>
+        <v>2.6529</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0529</v>
+        <v>0.0891</v>
       </c>
       <c r="H9" t="n">
-        <v>4.069</v>
+        <v>3.8586</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1157</v>
+        <v>2.0836</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0529</v>
+        <v>0.0891</v>
       </c>
       <c r="K9" t="n">
         <v>45</v>
@@ -851,7 +851,7 @@
         <v>76</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1686</v>
+        <v>2.1727</v>
       </c>
       <c r="N9" t="n">
         <v>121</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6803</v>
+        <v>2.7112</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4318</v>
+        <v>0.4368</v>
       </c>
       <c r="D10" t="n">
-        <v>0.572</v>
+        <v>0.61</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6803</v>
+        <v>2.7112</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9498</v>
+        <v>2.8566</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2695</v>
+        <v>-0.1454</v>
       </c>
       <c r="H10" t="n">
-        <v>4.907</v>
+        <v>4.5308</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5514</v>
+        <v>2.4466</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2695</v>
+        <v>-0.1454</v>
       </c>
       <c r="K10" t="n">
         <v>125</v>
@@ -897,7 +897,7 @@
         <v>128</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2819</v>
+        <v>2.3012</v>
       </c>
       <c r="N10" t="n">
         <v>253</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6081</v>
+        <v>2.5012</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4202</v>
+        <v>0.4029</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5394</v>
+        <v>0.5144</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6081</v>
+        <v>2.5012</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1832</v>
+        <v>2.0369</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4249</v>
+        <v>0.4643</v>
       </c>
       <c r="H11" t="n">
-        <v>2.206</v>
+        <v>2.0369</v>
       </c>
       <c r="I11" t="n">
-        <v>1.147</v>
+        <v>1.0999</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4249</v>
+        <v>0.4643</v>
       </c>
       <c r="K11" t="n">
         <v>178</v>
@@ -943,7 +943,7 @@
         <v>53</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5719</v>
+        <v>1.5642</v>
       </c>
       <c r="N11" t="n">
         <v>231</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Friis</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4852</v>
+        <v>2.3973</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4004</v>
+        <v>0.3862</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4839</v>
+        <v>0.4671</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4852</v>
+        <v>2.3973</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4852</v>
+        <v>-0.5324</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2.9297</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4852</v>
+        <v>-0.5324</v>
       </c>
       <c r="I12" t="n">
-        <v>2.4852</v>
+        <v>-0.2875</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2.9297</v>
       </c>
       <c r="K12" t="n">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M12" t="n">
-        <v>2.4852</v>
+        <v>2.6422</v>
       </c>
       <c r="N12" t="n">
-        <v>104</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Friis</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2762</v>
+        <v>2.3101</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3667</v>
+        <v>0.3722</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3896</v>
+        <v>0.4274</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2762</v>
+        <v>2.3101</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5854</v>
+        <v>2.3101</v>
       </c>
       <c r="G13" t="n">
-        <v>2.8616</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5854</v>
+        <v>2.3311</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3044</v>
+        <v>2.3311</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8616</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L13" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5572</v>
+        <v>2.3311</v>
       </c>
       <c r="N13" t="n">
-        <v>253</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0944</v>
+        <v>1.9727</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3374</v>
+        <v>0.3178</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3075</v>
+        <v>0.2738</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0944</v>
+        <v>1.9727</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7137</v>
+        <v>2.6168</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6193</v>
+        <v>-0.6441</v>
       </c>
       <c r="H14" t="n">
-        <v>4.075</v>
+        <v>3.7395</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1188</v>
+        <v>2.0193</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6193</v>
+        <v>-0.6441</v>
       </c>
       <c r="K14" t="n">
         <v>178</v>
@@ -1081,7 +1081,7 @@
         <v>53</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4995</v>
+        <v>1.3752</v>
       </c>
       <c r="N14" t="n">
         <v>231</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9836</v>
+        <v>1.8623</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3196</v>
+        <v>0.3</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2575</v>
+        <v>0.2236</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9836</v>
+        <v>1.8623</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7926</v>
+        <v>2.719</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8090000000000001</v>
+        <v>-0.8567</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3531</v>
+        <v>4.0767</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2634</v>
+        <v>2.2014</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8090000000000001</v>
+        <v>-0.8567</v>
       </c>
       <c r="K15" t="n">
         <v>45</v>
@@ -1127,7 +1127,7 @@
         <v>76</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4544</v>
+        <v>1.3447</v>
       </c>
       <c r="N15" t="n">
         <v>121</v>
@@ -1136,231 +1136,231 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4715</v>
+        <v>1.4398</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2371</v>
+        <v>0.232</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0263</v>
+        <v>0.0312</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4715</v>
+        <v>1.4398</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4715</v>
+        <v>2.5903</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-1.1505</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4715</v>
+        <v>3.6521</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4715</v>
+        <v>1.9721</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-1.1505</v>
       </c>
       <c r="K16" t="n">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4715</v>
+        <v>0.8215999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>104</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SicK</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4146</v>
+        <v>1.3488</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2279</v>
+        <v>0.2173</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0102</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4146</v>
+        <v>1.3488</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8259</v>
+        <v>1.3488</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4113</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8259</v>
+        <v>1.3488</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9494</v>
+        <v>1.3488</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4113</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="L17" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5381</v>
+        <v>1.3488</v>
       </c>
       <c r="N17" t="n">
-        <v>231</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>SicK</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3424</v>
+        <v>1.2097</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2163</v>
+        <v>0.1949</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.032</v>
+        <v>-0.0735</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3424</v>
+        <v>1.2097</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6417</v>
+        <v>1.6532</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2993</v>
+        <v>-0.4435</v>
       </c>
       <c r="H18" t="n">
-        <v>3.8214</v>
+        <v>1.6532</v>
       </c>
       <c r="I18" t="n">
-        <v>1.987</v>
+        <v>0.8927</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2993</v>
+        <v>-0.4435</v>
       </c>
       <c r="K18" t="n">
-        <v>50</v>
+        <v>178</v>
       </c>
       <c r="L18" t="n">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6877000000000002</v>
+        <v>0.4492</v>
       </c>
       <c r="N18" t="n">
-        <v>155</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2408</v>
+        <v>1.1453</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1999</v>
+        <v>0.1845</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0779</v>
+        <v>-0.1028</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2408</v>
+        <v>1.1453</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0988</v>
+        <v>1.1453</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.858</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0988</v>
+        <v>1.1453</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0913</v>
+        <v>1.1453</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.858</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="L19" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2333</v>
+        <v>1.1453</v>
       </c>
       <c r="N19" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1217</v>
+        <v>1.0787</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1807</v>
+        <v>0.1738</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1316</v>
+        <v>-0.1332</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1217</v>
+        <v>1.0787</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1217</v>
+        <v>1.9837</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.905</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1217</v>
+        <v>1.9837</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1217</v>
+        <v>1.0712</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.905</v>
       </c>
       <c r="K20" t="n">
-        <v>115</v>
+        <v>45</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1217</v>
+        <v>0.1661999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1129</v>
+        <v>1.0607</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1793</v>
+        <v>0.1709</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1356</v>
+        <v>-0.1414</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1129</v>
+        <v>1.0607</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1129</v>
+        <v>1.0607</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1129</v>
+        <v>1.0607</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1129</v>
+        <v>1.0607</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1129</v>
+        <v>1.0607</v>
       </c>
       <c r="N21" t="n">
         <v>115</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0197</v>
+        <v>0.9444</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1643</v>
+        <v>0.1521</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1777</v>
+        <v>-0.1943</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0197</v>
+        <v>0.9444</v>
       </c>
       <c r="F22" t="n">
-        <v>1.397</v>
+        <v>0.9444</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3773</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.397</v>
+        <v>0.9444</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7264</v>
+        <v>0.9444</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3773</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>45</v>
+        <v>104</v>
       </c>
       <c r="L22" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3491</v>
+        <v>0.9444</v>
       </c>
       <c r="N22" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0119</v>
+        <v>0.9326</v>
       </c>
       <c r="C23" t="n">
-        <v>0.163</v>
+        <v>0.1502</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1812</v>
+        <v>-0.1997</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0119</v>
+        <v>0.9326</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0119</v>
+        <v>1.3276</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.395</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0119</v>
+        <v>1.3276</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0119</v>
+        <v>0.7169</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.395</v>
       </c>
       <c r="K23" t="n">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0119</v>
+        <v>0.3219</v>
       </c>
       <c r="N23" t="n">
-        <v>104</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9134</v>
+        <v>0.9038</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1471</v>
+        <v>0.1456</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2257</v>
+        <v>-0.2128</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9134</v>
+        <v>0.9038</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9134</v>
+        <v>0.9038</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9134</v>
+        <v>0.9038</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9134</v>
+        <v>0.9038</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9134</v>
+        <v>0.9038</v>
       </c>
       <c r="N24" t="n">
         <v>115</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7809</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1258</v>
+        <v>0.1126</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2855</v>
+        <v>-0.306</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7809</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7809</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7809</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7809</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7809</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="N25" t="n">
         <v>108</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6123</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0844</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3616</v>
+        <v>-0.3858</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6123</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6123</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6123</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6123</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6123</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="N26" t="n">
         <v>71</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.496</v>
+        <v>0.5053</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0799</v>
+        <v>0.0814</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4141</v>
+        <v>-0.3942</v>
       </c>
       <c r="E27" t="n">
-        <v>0.496</v>
+        <v>0.5053</v>
       </c>
       <c r="F27" t="n">
-        <v>0.496</v>
+        <v>0.1717</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.3336</v>
       </c>
       <c r="H27" t="n">
-        <v>0.496</v>
+        <v>0.1717</v>
       </c>
       <c r="I27" t="n">
-        <v>0.496</v>
+        <v>0.0927</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.3336</v>
       </c>
       <c r="K27" t="n">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M27" t="n">
-        <v>0.496</v>
+        <v>0.4263</v>
       </c>
       <c r="N27" t="n">
-        <v>108</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3942</v>
+        <v>0.4508</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0635</v>
+        <v>0.0726</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4601</v>
+        <v>-0.419</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3942</v>
+        <v>0.4508</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1267</v>
+        <v>0.4508</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2675</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1267</v>
+        <v>0.4508</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0659</v>
+        <v>0.4508</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2675</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="L28" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3334</v>
+        <v>0.4508</v>
       </c>
       <c r="N28" t="n">
-        <v>155</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3011</v>
+        <v>0.267</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0485</v>
+        <v>0.043</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5021</v>
+        <v>-0.5027</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3011</v>
+        <v>0.267</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3011</v>
+        <v>0.267</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3011</v>
+        <v>0.267</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3011</v>
+        <v>0.267</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3011</v>
+        <v>0.267</v>
       </c>
       <c r="N29" t="n">
         <v>71</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0173</v>
+        <v>0.0155</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0028</v>
+        <v>0.0025</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6302</v>
+        <v>-0.6171</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0173</v>
+        <v>0.0155</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0173</v>
+        <v>0.0155</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0173</v>
+        <v>0.0155</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0173</v>
+        <v>0.0155</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0173</v>
+        <v>0.0155</v>
       </c>
       <c r="N30" t="n">
         <v>115</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0136</v>
+        <v>-0.0414</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0022</v>
+        <v>-0.0067</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6442</v>
+        <v>-0.643</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0136</v>
+        <v>-0.0414</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0136</v>
+        <v>-0.0414</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0136</v>
+        <v>-0.0414</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0136</v>
+        <v>-0.0414</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0136</v>
+        <v>-0.0414</v>
       </c>
       <c r="N31" t="n">
         <v>104</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0887</v>
+        <v>-0.1062</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0143</v>
+        <v>-0.0171</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6781</v>
+        <v>-0.6725</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0887</v>
+        <v>-0.1062</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0887</v>
+        <v>-0.1062</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0887</v>
+        <v>-0.1062</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0887</v>
+        <v>-0.1062</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.0887</v>
+        <v>-0.1062</v>
       </c>
       <c r="N32" t="n">
         <v>115</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.1131</v>
+        <v>-0.1341</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0182</v>
+        <v>-0.0216</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6891</v>
+        <v>-0.6852</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.1131</v>
+        <v>-0.1341</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1131</v>
+        <v>-0.1341</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1131</v>
+        <v>-0.1341</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1131</v>
+        <v>-0.1341</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.1131</v>
+        <v>-0.1341</v>
       </c>
       <c r="N33" t="n">
         <v>71</v>
@@ -1964,231 +1964,231 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>HUNDEN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.2504</v>
+        <v>-0.2952</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0403</v>
+        <v>-0.0476</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7511</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.2504</v>
+        <v>-0.2952</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2504</v>
+        <v>-0.2952</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2504</v>
+        <v>-0.2952</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2504</v>
+        <v>-0.2952</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2504</v>
+        <v>-0.2952</v>
       </c>
       <c r="N34" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HUNDEN</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.252</v>
+        <v>-0.3004</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0406</v>
+        <v>-0.0484</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7518</v>
+        <v>-0.761</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.252</v>
+        <v>-0.3004</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.252</v>
+        <v>-0.3004</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.252</v>
+        <v>-0.3004</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.252</v>
+        <v>-0.3004</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.252</v>
+        <v>-0.3004</v>
       </c>
       <c r="N35" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.4421</v>
+        <v>-0.4026</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0712</v>
+        <v>-0.0649</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8376</v>
+        <v>-0.8075</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.4421</v>
+        <v>-0.4026</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4421</v>
+        <v>-1.2709</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.8683</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4421</v>
+        <v>-1.2709</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4421</v>
+        <v>-0.6863</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.8683</v>
       </c>
       <c r="K36" t="n">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.4421</v>
+        <v>0.1819999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>108</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.6456</v>
+        <v>-0.4516</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.104</v>
+        <v>-0.0728</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9295</v>
+        <v>-0.8298</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.6456</v>
+        <v>-0.4516</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.6456</v>
+        <v>-0.4516</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.6456</v>
+        <v>-0.4516</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6456</v>
+        <v>-0.4516</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6456</v>
+        <v>-0.4516</v>
       </c>
       <c r="N37" t="n">
-        <v>71</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.7671</v>
+        <v>-0.7008</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1236</v>
+        <v>-0.1129</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9843</v>
+        <v>-0.9432</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.7671</v>
+        <v>-0.7008</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.5269</v>
+        <v>-0.7008</v>
       </c>
       <c r="G38" t="n">
-        <v>0.7598</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.5269</v>
+        <v>-0.7008</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-0.7008</v>
       </c>
       <c r="J38" t="n">
-        <v>0.7598</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="L38" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.03410000000000002</v>
+        <v>-0.7008</v>
       </c>
       <c r="N38" t="n">
-        <v>155</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.8873</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1429</v>
+        <v>-0.1462</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0386</v>
+        <v>-1.0375</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.8873</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.8873</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.8873</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.8873</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.8873</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="N39" t="n">
         <v>108</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3156</v>
+        <v>-1.3406</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2119</v>
+        <v>-0.216</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2319</v>
+        <v>-1.2345</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3156</v>
+        <v>-1.3406</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3156</v>
+        <v>-1.3406</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3156</v>
+        <v>-1.3406</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3156</v>
+        <v>-1.3406</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3156</v>
+        <v>-1.3406</v>
       </c>
       <c r="N40" t="n">
         <v>71</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.8115</v>
+        <v>-3.5481</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.614</v>
+        <v>-0.5716</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.3587</v>
+        <v>-2.2394</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.8115</v>
+        <v>-3.5481</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.071</v>
+        <v>-2.7826</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.7405</v>
+        <v>-0.7655</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.071</v>
+        <v>-2.7826</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.5968</v>
+        <v>-1.5026</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.7405</v>
+        <v>-0.7655</v>
       </c>
       <c r="K41" t="n">
         <v>178</v>
@@ -2323,7 +2323,7 @@
         <v>53</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.3373</v>
+        <v>-2.2681</v>
       </c>
       <c r="N41" t="n">
         <v>231</v>
@@ -2429,10 +2429,10 @@
         <v>1.12</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4212</v>
+        <v>0.3902</v>
       </c>
       <c r="J2" t="n">
-        <v>9.266400000000001</v>
+        <v>8.5844</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3079</v>
+        <v>-0.3273</v>
       </c>
       <c r="J3" t="n">
-        <v>-6.7738</v>
+        <v>-7.2006</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.62</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3728</v>
+        <v>-0.3898</v>
       </c>
       <c r="J4" t="n">
-        <v>-8.201599999999999</v>
+        <v>-8.5756</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.62</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3728</v>
+        <v>-0.3898</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.201599999999999</v>
+        <v>-8.5756</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.52</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4663</v>
+        <v>-0.4783</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.2586</v>
+        <v>-10.5226</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.75</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4143</v>
+        <v>1.5309</v>
       </c>
       <c r="J7" t="n">
-        <v>31.1146</v>
+        <v>33.6798</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.32</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8112</v>
+        <v>0.7739</v>
       </c>
       <c r="J8" t="n">
-        <v>17.8464</v>
+        <v>17.0258</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.32</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8112</v>
+        <v>0.7739</v>
       </c>
       <c r="J9" t="n">
-        <v>17.8464</v>
+        <v>17.0258</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.27</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6994</v>
+        <v>0.675</v>
       </c>
       <c r="J10" t="n">
-        <v>15.3868</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0859</v>
+        <v>0.1146</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8898</v>
+        <v>2.5212</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.23</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4765</v>
+        <v>0.4719</v>
       </c>
       <c r="J12" t="n">
-        <v>14.295</v>
+        <v>14.157</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.11</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2544</v>
+        <v>0.2631</v>
       </c>
       <c r="J13" t="n">
-        <v>7.632</v>
+        <v>7.893</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.08</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1943</v>
+        <v>0.2048</v>
       </c>
       <c r="J14" t="n">
-        <v>5.829</v>
+        <v>6.144</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.97</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0553</v>
+        <v>-0.0622</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.659</v>
+        <v>-1.866</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.88</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1622</v>
+        <v>-0.174</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.866</v>
+        <v>-5.22</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.32</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9006</v>
+        <v>0.8361</v>
       </c>
       <c r="J17" t="n">
-        <v>27.018</v>
+        <v>25.083</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7544</v>
+        <v>0.7084</v>
       </c>
       <c r="J18" t="n">
-        <v>22.632</v>
+        <v>21.252</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3637</v>
+        <v>0.3586</v>
       </c>
       <c r="J19" t="n">
-        <v>10.911</v>
+        <v>10.758</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.84</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5279</v>
+        <v>-0.5018</v>
       </c>
       <c r="J20" t="n">
-        <v>-15.837</v>
+        <v>-15.054</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.68</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9346</v>
+        <v>-0.8599</v>
       </c>
       <c r="J21" t="n">
-        <v>-28.038</v>
+        <v>-25.797</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.01</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.0851</v>
       </c>
       <c r="J22" t="n">
-        <v>2.2848</v>
+        <v>2.0424</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.9</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.112</v>
+        <v>-0.1299</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.688</v>
+        <v>-3.1176</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.72</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2921</v>
+        <v>-0.3095</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.0104</v>
+        <v>-7.428</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.7</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3111</v>
+        <v>-0.328</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.4664</v>
+        <v>-7.872</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3206</v>
+        <v>-0.3372</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.6944</v>
+        <v>-8.0928</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.41</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7331</v>
+        <v>0.8154</v>
       </c>
       <c r="J27" t="n">
-        <v>17.5944</v>
+        <v>19.5696</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.35</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6565</v>
+        <v>0.7315</v>
       </c>
       <c r="J28" t="n">
-        <v>15.756</v>
+        <v>17.556</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.33</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6309</v>
+        <v>0.7032</v>
       </c>
       <c r="J29" t="n">
-        <v>15.1416</v>
+        <v>16.8768</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.24</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5129</v>
+        <v>0.5715</v>
       </c>
       <c r="J30" t="n">
-        <v>12.3096</v>
+        <v>13.716</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.17</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4121</v>
+        <v>0.4576</v>
       </c>
       <c r="J31" t="n">
-        <v>9.8904</v>
+        <v>10.9824</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.5</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.6017</v>
       </c>
       <c r="J32" t="n">
-        <v>15.921</v>
+        <v>18.051</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1411</v>
+        <v>0.1542</v>
       </c>
       <c r="J33" t="n">
-        <v>4.233</v>
+        <v>4.626</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.079</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>2.37</v>
+        <v>2.697</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.79</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2527</v>
+        <v>-0.2652</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.581</v>
+        <v>-7.956</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.75</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2919</v>
+        <v>-0.3038</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.757</v>
+        <v>-9.114000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4485</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>13.455</v>
+        <v>15.045</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.15</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2491</v>
+        <v>0.2601</v>
       </c>
       <c r="J38" t="n">
-        <v>7.473</v>
+        <v>7.803</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1147</v>
+        <v>0.1266</v>
       </c>
       <c r="J39" t="n">
-        <v>3.441</v>
+        <v>3.798</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.1055</v>
       </c>
       <c r="J40" t="n">
-        <v>-2.898</v>
+        <v>-3.165</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.89</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1541</v>
+        <v>-0.1651</v>
       </c>
       <c r="J41" t="n">
-        <v>-4.623</v>
+        <v>-4.953</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.09</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2938</v>
+        <v>0.2824</v>
       </c>
       <c r="J42" t="n">
-        <v>6.4636</v>
+        <v>6.2128</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.86</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1572</v>
+        <v>-0.1754</v>
       </c>
       <c r="J43" t="n">
-        <v>-3.4584</v>
+        <v>-3.8588</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.77</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2452</v>
+        <v>-0.2635</v>
       </c>
       <c r="J44" t="n">
-        <v>-5.3944</v>
+        <v>-5.797</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.74</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.274</v>
+        <v>-0.2917</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.028</v>
+        <v>-6.4174</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.6</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4064</v>
+        <v>-0.4193</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.940799999999999</v>
+        <v>-9.224600000000001</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.53</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8812</v>
+        <v>0.9761</v>
       </c>
       <c r="J47" t="n">
-        <v>19.3864</v>
+        <v>21.4742</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.48</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8192</v>
+        <v>0.9093</v>
       </c>
       <c r="J48" t="n">
-        <v>18.0224</v>
+        <v>20.0046</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.39</v>
       </c>
       <c r="I49" t="n">
-        <v>0.706</v>
+        <v>0.7862</v>
       </c>
       <c r="J49" t="n">
-        <v>15.532</v>
+        <v>17.2964</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.2</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4548</v>
+        <v>0.5067</v>
       </c>
       <c r="J50" t="n">
-        <v>10.0056</v>
+        <v>11.1474</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.96</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2438</v>
+        <v>-0.2242</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.3636</v>
+        <v>-4.9324</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.38</v>
       </c>
       <c r="I52" t="n">
-        <v>0.723</v>
+        <v>0.7982</v>
       </c>
       <c r="J52" t="n">
-        <v>21.69</v>
+        <v>23.946</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.24</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5302</v>
+        <v>0.5864</v>
       </c>
       <c r="J53" t="n">
-        <v>15.906</v>
+        <v>17.592</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.15</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>0.4367</v>
       </c>
       <c r="J54" t="n">
-        <v>12</v>
+        <v>13.101</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0353</v>
+        <v>-0.0243</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.059</v>
+        <v>-0.729</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.97</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1686</v>
+        <v>-0.1622</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.058</v>
+        <v>-4.866</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.31</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5153</v>
+        <v>0.5716</v>
       </c>
       <c r="J57" t="n">
-        <v>15.459</v>
+        <v>17.148</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.26</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4634</v>
+        <v>0.5123</v>
       </c>
       <c r="J58" t="n">
-        <v>13.902</v>
+        <v>15.369</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.86</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1754</v>
+        <v>-0.1893</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.262</v>
+        <v>-5.679</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.86</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1754</v>
+        <v>-0.1893</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.262</v>
+        <v>-5.679</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.62</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.409</v>
+        <v>-0.4181</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.27</v>
+        <v>-12.543</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.71</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1069</v>
+        <v>1.2155</v>
       </c>
       <c r="J62" t="n">
-        <v>25.4587</v>
+        <v>27.9565</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.51</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8618</v>
+        <v>0.9542</v>
       </c>
       <c r="J63" t="n">
-        <v>19.8214</v>
+        <v>21.9466</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.43</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7611</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>17.5053</v>
+        <v>19.4419</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.24</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5147</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="J65" t="n">
-        <v>11.8381</v>
+        <v>13.1813</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.53</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.3361</v>
+        <v>-1.1977</v>
       </c>
       <c r="J66" t="n">
-        <v>-30.7303</v>
+        <v>-27.5471</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.13</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3606</v>
+        <v>0.3631</v>
       </c>
       <c r="J67" t="n">
-        <v>8.293799999999999</v>
+        <v>8.3513</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.92</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.1073</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.0792</v>
+        <v>-2.4679</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.78</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2359</v>
+        <v>-0.2542</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.4257</v>
+        <v>-5.8466</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.68</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3315</v>
+        <v>-0.3474</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.6245</v>
+        <v>-7.9902</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4439</v>
+        <v>-0.4548</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.2097</v>
+        <v>-10.4604</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.41</v>
       </c>
       <c r="I72" t="n">
-        <v>0.87</v>
+        <v>0.8148</v>
       </c>
       <c r="J72" t="n">
-        <v>23.49</v>
+        <v>21.9996</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.09</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2643</v>
+        <v>0.2607</v>
       </c>
       <c r="J73" t="n">
-        <v>7.1361</v>
+        <v>7.0389</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.74</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2829</v>
+        <v>-0.2986</v>
       </c>
       <c r="J74" t="n">
-        <v>-7.6383</v>
+        <v>-8.062200000000001</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.65</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3686</v>
+        <v>-0.3816</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.952199999999999</v>
+        <v>-10.3032</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.5</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.507</v>
+        <v>-0.5131</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.689</v>
+        <v>-13.8537</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.4</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9981</v>
+        <v>0.9426</v>
       </c>
       <c r="J77" t="n">
-        <v>26.9487</v>
+        <v>25.4502</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.34</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8767</v>
+        <v>0.8273</v>
       </c>
       <c r="J78" t="n">
-        <v>23.6709</v>
+        <v>22.3371</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.32</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8316</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>22.4532</v>
+        <v>21.2706</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.21</v>
       </c>
       <c r="I80" t="n">
-        <v>0.5799</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J80" t="n">
-        <v>15.6573</v>
+        <v>15.228</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.87</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4952</v>
+        <v>-0.4625</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.3704</v>
+        <v>-12.4875</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.33</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7581</v>
+        <v>0.7103</v>
       </c>
       <c r="J82" t="n">
-        <v>18.9525</v>
+        <v>17.7575</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.06</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2166</v>
+        <v>0.2102</v>
       </c>
       <c r="J83" t="n">
-        <v>5.415</v>
+        <v>5.255</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.76</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2572</v>
+        <v>-0.2747</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.43</v>
+        <v>-6.8675</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.55</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4553</v>
+        <v>-0.4652</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.3825</v>
+        <v>-11.63</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.45</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-0.5514</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.6725</v>
+        <v>-13.785</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.7</v>
       </c>
       <c r="I87" t="n">
-        <v>1.3656</v>
+        <v>1.3473</v>
       </c>
       <c r="J87" t="n">
-        <v>34.14</v>
+        <v>33.6825</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.28</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7298</v>
+        <v>0.7004</v>
       </c>
       <c r="J88" t="n">
-        <v>18.245</v>
+        <v>17.51</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.26</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6847</v>
+        <v>0.6602</v>
       </c>
       <c r="J89" t="n">
-        <v>17.1175</v>
+        <v>16.505</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.13</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3628</v>
+        <v>0.3707</v>
       </c>
       <c r="J90" t="n">
-        <v>9.07</v>
+        <v>9.2675</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.11</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3081</v>
+        <v>0.3205</v>
       </c>
       <c r="J91" t="n">
-        <v>7.7025</v>
+        <v>8.012499999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.37</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4826</v>
+        <v>0.492</v>
       </c>
       <c r="J92" t="n">
-        <v>11.0998</v>
+        <v>11.316</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.31</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4136</v>
+        <v>0.4264</v>
       </c>
       <c r="J93" t="n">
-        <v>9.5128</v>
+        <v>9.8072</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.23</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3192</v>
+        <v>0.3355</v>
       </c>
       <c r="J94" t="n">
-        <v>7.3416</v>
+        <v>7.7165</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.05</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0791</v>
+        <v>0.0949</v>
       </c>
       <c r="J95" t="n">
-        <v>1.8193</v>
+        <v>2.1827</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1068</v>
+        <v>-0.1135</v>
       </c>
       <c r="J96" t="n">
-        <v>-2.4564</v>
+        <v>-2.6105</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.26</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4302</v>
+        <v>0.4266</v>
       </c>
       <c r="J97" t="n">
-        <v>9.894600000000001</v>
+        <v>9.8118</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2734</v>
+        <v>0.2782</v>
       </c>
       <c r="J98" t="n">
-        <v>6.2882</v>
+        <v>6.3986</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.84</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1936</v>
+        <v>-0.2083</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.4528</v>
+        <v>-4.7909</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.83</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2039</v>
+        <v>-0.2185</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.6897</v>
+        <v>-5.0255</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.72</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3125</v>
+        <v>-0.3255</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.1875</v>
+        <v>-7.4865</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.26</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5823</v>
+        <v>0.5595</v>
       </c>
       <c r="J102" t="n">
-        <v>14.5575</v>
+        <v>13.9875</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.93</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0925</v>
+        <v>-0.1058</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.3125</v>
+        <v>-2.645</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.9</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1253</v>
+        <v>-0.1401</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.1325</v>
+        <v>-3.5025</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.77</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2583</v>
+        <v>-0.2736</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.4575</v>
+        <v>-6.84</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.71</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3164</v>
+        <v>-0.3304</v>
       </c>
       <c r="J106" t="n">
-        <v>-7.91</v>
+        <v>-8.26</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.77</v>
       </c>
       <c r="I107" t="n">
-        <v>1.484</v>
+        <v>1.4666</v>
       </c>
       <c r="J107" t="n">
-        <v>37.1</v>
+        <v>36.665</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.58</v>
       </c>
       <c r="I108" t="n">
-        <v>1.2475</v>
+        <v>1.2168</v>
       </c>
       <c r="J108" t="n">
-        <v>31.1875</v>
+        <v>30.42</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.11</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3341</v>
+        <v>0.3385</v>
       </c>
       <c r="J109" t="n">
-        <v>8.352499999999999</v>
+        <v>8.4625</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.78</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.7225</v>
+        <v>-0.6681</v>
       </c>
       <c r="J110" t="n">
-        <v>-18.0625</v>
+        <v>-16.7025</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.68</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.9693000000000001</v>
+        <v>-0.8844</v>
       </c>
       <c r="J111" t="n">
-        <v>-24.2325</v>
+        <v>-22.11</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.8</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.1763</v>
+        <v>-0.2038</v>
       </c>
       <c r="J112" t="n">
-        <v>-3.526</v>
+        <v>-4.076</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.75</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2307</v>
+        <v>-0.2563</v>
       </c>
       <c r="J113" t="n">
-        <v>-4.614</v>
+        <v>-5.126</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.64</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3404</v>
+        <v>-0.3614</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.808</v>
+        <v>-7.228</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.46</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5054</v>
+        <v>-0.5174</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.108</v>
+        <v>-10.348</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.42</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5434</v>
+        <v>-0.5526</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.868</v>
+        <v>-11.052</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.86</v>
       </c>
       <c r="I117" t="n">
-        <v>1.5095</v>
+        <v>1.5066</v>
       </c>
       <c r="J117" t="n">
-        <v>30.19</v>
+        <v>30.132</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.52</v>
       </c>
       <c r="I118" t="n">
-        <v>1.1181</v>
+        <v>1.0889</v>
       </c>
       <c r="J118" t="n">
-        <v>22.362</v>
+        <v>21.778</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.51</v>
       </c>
       <c r="I119" t="n">
-        <v>1.1065</v>
+        <v>1.0761</v>
       </c>
       <c r="J119" t="n">
-        <v>22.13</v>
+        <v>21.522</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.48</v>
       </c>
       <c r="I120" t="n">
-        <v>1.072</v>
+        <v>1.0367</v>
       </c>
       <c r="J120" t="n">
-        <v>21.44</v>
+        <v>20.734</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.06</v>
       </c>
       <c r="I121" t="n">
-        <v>0.12</v>
+        <v>0.1548</v>
       </c>
       <c r="J121" t="n">
-        <v>2.4</v>
+        <v>3.096</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.52</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1852</v>
+        <v>1.1477</v>
       </c>
       <c r="J122" t="n">
-        <v>30.8152</v>
+        <v>29.8402</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.31</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8378</v>
+        <v>0.788</v>
       </c>
       <c r="J123" t="n">
-        <v>21.7828</v>
+        <v>20.488</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.08</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2603</v>
+        <v>0.2674</v>
       </c>
       <c r="J124" t="n">
-        <v>6.7678</v>
+        <v>6.9524</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.93</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2968</v>
+        <v>-0.2851</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.7168</v>
+        <v>-7.4126</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.83</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5437</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.0826</v>
+        <v>-14.1362</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.54</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="J127" t="n">
-        <v>25.7244</v>
+        <v>24.466</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.06</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1548</v>
+        <v>0.1651</v>
       </c>
       <c r="J128" t="n">
-        <v>4.0248</v>
+        <v>4.2926</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.05</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1328</v>
+        <v>0.1433</v>
       </c>
       <c r="J129" t="n">
-        <v>3.4528</v>
+        <v>3.7258</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.86</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1818</v>
+        <v>-0.1943</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.7268</v>
+        <v>-5.0518</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3592</v>
+        <v>-0.3692</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.3392</v>
+        <v>-9.5992</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.46</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0825</v>
+        <v>1.0407</v>
       </c>
       <c r="J132" t="n">
-        <v>25.98</v>
+        <v>24.9768</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.34</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8751</v>
+        <v>0.8262</v>
       </c>
       <c r="J133" t="n">
-        <v>21.0024</v>
+        <v>19.8288</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.22</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6025</v>
+        <v>0.5845</v>
       </c>
       <c r="J134" t="n">
-        <v>14.46</v>
+        <v>14.028</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.22</v>
       </c>
       <c r="I135" t="n">
-        <v>0.6025</v>
+        <v>0.5845</v>
       </c>
       <c r="J135" t="n">
-        <v>14.46</v>
+        <v>14.028</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.93</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3223</v>
+        <v>-0.303</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.7352</v>
+        <v>-7.272</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.23</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5669</v>
+        <v>0.5384</v>
       </c>
       <c r="J137" t="n">
-        <v>13.6056</v>
+        <v>12.9216</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.99</v>
       </c>
       <c r="I138" t="n">
-        <v>0.0022</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="J138" t="n">
-        <v>0.0528</v>
+        <v>-0.2016</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.74</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2773</v>
+        <v>-0.2942</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.6552</v>
+        <v>-7.0608</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.72</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2965</v>
+        <v>-0.313</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.116</v>
+        <v>-7.512</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.5</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.502</v>
+        <v>-0.5092</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.048</v>
+        <v>-12.2208</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.2</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.5659</v>
       </c>
       <c r="J142" t="n">
-        <v>24.1982</v>
+        <v>23.2019</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.18</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5393</v>
+        <v>0.5203</v>
       </c>
       <c r="J143" t="n">
-        <v>22.1113</v>
+        <v>21.3323</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.15</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4614</v>
+        <v>0.4501</v>
       </c>
       <c r="J144" t="n">
-        <v>18.9174</v>
+        <v>18.4541</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.13</v>
       </c>
       <c r="I145" t="n">
-        <v>0.4083</v>
+        <v>0.4018</v>
       </c>
       <c r="J145" t="n">
-        <v>16.7403</v>
+        <v>16.4738</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.8214</v>
+        <v>-0.7598</v>
       </c>
       <c r="J146" t="n">
-        <v>-33.6774</v>
+        <v>-31.1518</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.28</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5571</v>
+        <v>0.5472</v>
       </c>
       <c r="J147" t="n">
-        <v>22.8411</v>
+        <v>22.4352</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.12</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2697</v>
+        <v>0.2787</v>
       </c>
       <c r="J148" t="n">
-        <v>11.0577</v>
+        <v>11.4267</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.03</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0814</v>
+        <v>0.0926</v>
       </c>
       <c r="J149" t="n">
-        <v>3.3374</v>
+        <v>3.7966</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.99</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.0275</v>
+        <v>-0.0305</v>
       </c>
       <c r="J150" t="n">
-        <v>-1.1275</v>
+        <v>-1.2505</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.96</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.0709</v>
+        <v>-0.0785</v>
       </c>
       <c r="J151" t="n">
-        <v>-2.9069</v>
+        <v>-3.2185</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.82</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.1592</v>
+        <v>-0.1861</v>
       </c>
       <c r="J152" t="n">
-        <v>-3.184</v>
+        <v>-3.722</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.67</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3152</v>
+        <v>-0.3367</v>
       </c>
       <c r="J153" t="n">
-        <v>-6.304</v>
+        <v>-6.734</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.64</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3428</v>
+        <v>-0.3633</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.856</v>
+        <v>-7.266</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.52</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4518</v>
+        <v>-0.4669</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.036</v>
+        <v>-9.337999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.5</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4706</v>
+        <v>-0.4845</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.412000000000001</v>
+        <v>-9.69</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.84</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9083</v>
+        <v>0.8983</v>
       </c>
       <c r="J157" t="n">
-        <v>18.166</v>
+        <v>17.966</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.73</v>
       </c>
       <c r="I158" t="n">
-        <v>0.8032</v>
+        <v>0.8012</v>
       </c>
       <c r="J158" t="n">
-        <v>16.064</v>
+        <v>16.024</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.47</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5495</v>
+        <v>0.5633</v>
       </c>
       <c r="J159" t="n">
-        <v>10.99</v>
+        <v>11.266</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.41</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4867</v>
+        <v>0.5038</v>
       </c>
       <c r="J160" t="n">
-        <v>9.734</v>
+        <v>10.076</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.3</v>
       </c>
       <c r="I161" t="n">
-        <v>0.3652</v>
+        <v>0.3877</v>
       </c>
       <c r="J161" t="n">
-        <v>7.304</v>
+        <v>7.754</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.36</v>
       </c>
       <c r="I162" t="n">
-        <v>0.9516</v>
+        <v>0.8897</v>
       </c>
       <c r="J162" t="n">
-        <v>26.6448</v>
+        <v>24.9116</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.3</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.7679</v>
       </c>
       <c r="J163" t="n">
-        <v>22.82</v>
+        <v>21.5012</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.11</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3451</v>
+        <v>0.346</v>
       </c>
       <c r="J164" t="n">
-        <v>9.662800000000001</v>
+        <v>9.688000000000001</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1994</v>
+        <v>-0.193</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.5832</v>
+        <v>-5.404</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.93</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2963</v>
+        <v>-0.2848</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.2964</v>
+        <v>-7.9744</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.03</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1152</v>
+        <v>0.1169</v>
       </c>
       <c r="J167" t="n">
-        <v>3.2256</v>
+        <v>3.2732</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.02</v>
       </c>
       <c r="I168" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0895</v>
       </c>
       <c r="J168" t="n">
-        <v>2.4752</v>
+        <v>2.506</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.85</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1768</v>
+        <v>-0.1928</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.9504</v>
+        <v>-5.3984</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.82</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2073</v>
+        <v>-0.2234</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.8044</v>
+        <v>-6.2552</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2274</v>
+        <v>-0.2433</v>
       </c>
       <c r="J171" t="n">
-        <v>-6.3672</v>
+        <v>-6.8124</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.46</v>
       </c>
       <c r="I172" t="n">
-        <v>0.9213</v>
+        <v>0.8659</v>
       </c>
       <c r="J172" t="n">
-        <v>26.7177</v>
+        <v>25.1111</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.09</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2443</v>
+        <v>0.2461</v>
       </c>
       <c r="J173" t="n">
-        <v>7.0847</v>
+        <v>7.1369</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2211</v>
+        <v>-0.2363</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.4119</v>
+        <v>-6.8527</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.66</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3663</v>
+        <v>-0.3781</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.6227</v>
+        <v>-10.9649</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.65</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3756</v>
+        <v>-0.3871</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.8924</v>
+        <v>-11.2259</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.39</v>
       </c>
       <c r="I177" t="n">
-        <v>1.0007</v>
+        <v>0.9413</v>
       </c>
       <c r="J177" t="n">
-        <v>29.0203</v>
+        <v>27.2977</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.33</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8766</v>
+        <v>0.8232</v>
       </c>
       <c r="J178" t="n">
-        <v>25.4214</v>
+        <v>23.8728</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.18</v>
       </c>
       <c r="I179" t="n">
-        <v>0.5189</v>
+        <v>0.5063</v>
       </c>
       <c r="J179" t="n">
-        <v>15.0481</v>
+        <v>14.6827</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.17</v>
       </c>
       <c r="I180" t="n">
-        <v>0.4942</v>
+        <v>0.4839</v>
       </c>
       <c r="J180" t="n">
-        <v>14.3318</v>
+        <v>14.0331</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.71</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.8902</v>
+        <v>-0.8166</v>
       </c>
       <c r="J181" t="n">
-        <v>-25.8158</v>
+        <v>-23.6814</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.85</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.0961</v>
+        <v>-0.1298</v>
       </c>
       <c r="J182" t="n">
-        <v>-1.8259</v>
+        <v>-2.4662</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.72</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2458</v>
+        <v>-0.2737</v>
       </c>
       <c r="J183" t="n">
-        <v>-4.6702</v>
+        <v>-5.2003</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.53</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.4298</v>
+        <v>-0.4483</v>
       </c>
       <c r="J184" t="n">
-        <v>-8.1662</v>
+        <v>-8.5177</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.39</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.5623</v>
+        <v>-0.5714</v>
       </c>
       <c r="J185" t="n">
-        <v>-10.6837</v>
+        <v>-10.8566</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.32</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6304</v>
+        <v>-0.6338</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.9776</v>
+        <v>-12.0422</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.78</v>
       </c>
       <c r="I187" t="n">
-        <v>1.4142</v>
+        <v>1.4068</v>
       </c>
       <c r="J187" t="n">
-        <v>26.8698</v>
+        <v>26.7292</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.58</v>
       </c>
       <c r="I188" t="n">
-        <v>1.1852</v>
+        <v>1.162</v>
       </c>
       <c r="J188" t="n">
-        <v>22.5188</v>
+        <v>22.078</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.48</v>
       </c>
       <c r="I189" t="n">
-        <v>1.0701</v>
+        <v>1.0349</v>
       </c>
       <c r="J189" t="n">
-        <v>20.3319</v>
+        <v>19.6631</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.41</v>
       </c>
       <c r="I190" t="n">
-        <v>0.969</v>
+        <v>0.9227</v>
       </c>
       <c r="J190" t="n">
-        <v>18.411</v>
+        <v>17.5313</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.31</v>
       </c>
       <c r="I191" t="n">
-        <v>0.7564</v>
+        <v>0.7319</v>
       </c>
       <c r="J191" t="n">
-        <v>14.3716</v>
+        <v>13.9061</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.82</v>
       </c>
       <c r="I192" t="n">
-        <v>1.4721</v>
+        <v>1.4658</v>
       </c>
       <c r="J192" t="n">
-        <v>30.9141</v>
+        <v>30.7818</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.78</v>
       </c>
       <c r="I193" t="n">
-        <v>1.4263</v>
+        <v>1.4174</v>
       </c>
       <c r="J193" t="n">
-        <v>29.9523</v>
+        <v>29.7654</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.67</v>
       </c>
       <c r="I194" t="n">
-        <v>1.2989</v>
+        <v>1.2822</v>
       </c>
       <c r="J194" t="n">
-        <v>27.2769</v>
+        <v>26.9262</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.05</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0963</v>
+        <v>0.1303</v>
       </c>
       <c r="J195" t="n">
-        <v>2.0223</v>
+        <v>2.7363</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.91</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4283</v>
+        <v>-0.3912</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.994300000000001</v>
+        <v>-8.215199999999999</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.98</v>
       </c>
       <c r="I197" t="n">
-        <v>0.0382</v>
+        <v>0.0027</v>
       </c>
       <c r="J197" t="n">
-        <v>0.8022</v>
+        <v>0.0567</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.89</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.0998</v>
+        <v>-0.1231</v>
       </c>
       <c r="J198" t="n">
-        <v>-2.0958</v>
+        <v>-2.5851</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.73</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2701</v>
+        <v>-0.2908</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.6721</v>
+        <v>-6.1068</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.59</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3986</v>
+        <v>-0.4147</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.3706</v>
+        <v>-8.7087</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.31</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6599</v>
+        <v>-0.6584</v>
       </c>
       <c r="J201" t="n">
-        <v>-13.8579</v>
+        <v>-13.8264</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.07</v>
       </c>
       <c r="I202" t="n">
-        <v>0.2141</v>
+        <v>0.2138</v>
       </c>
       <c r="J202" t="n">
-        <v>5.5666</v>
+        <v>5.5588</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0225</v>
+        <v>0.0162</v>
       </c>
       <c r="J203" t="n">
-        <v>0.585</v>
+        <v>0.4212</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.85</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1757</v>
+        <v>-0.192</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.5682</v>
+        <v>-4.992</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.85</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1757</v>
+        <v>-0.192</v>
       </c>
       <c r="J205" t="n">
-        <v>-4.5682</v>
+        <v>-4.992</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.7</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3234</v>
+        <v>-0.3376</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.4084</v>
+        <v>-8.7776</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.91</v>
       </c>
       <c r="I207" t="n">
-        <v>1.6056</v>
+        <v>1.6011</v>
       </c>
       <c r="J207" t="n">
-        <v>41.7456</v>
+        <v>41.6286</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.47</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0782</v>
+        <v>1.0394</v>
       </c>
       <c r="J208" t="n">
-        <v>28.0332</v>
+        <v>27.0244</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.27</v>
       </c>
       <c r="I209" t="n">
-        <v>0.7020999999999999</v>
+        <v>0.6768</v>
       </c>
       <c r="J209" t="n">
-        <v>18.2546</v>
+        <v>17.5968</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.05</v>
       </c>
       <c r="I210" t="n">
-        <v>0.1223</v>
+        <v>0.1485</v>
       </c>
       <c r="J210" t="n">
-        <v>3.1798</v>
+        <v>3.861</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.93</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3437</v>
+        <v>-0.318</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.936199999999999</v>
+        <v>-8.268000000000001</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.1838</v>
+        <v>-0.2075</v>
       </c>
       <c r="J212" t="n">
-        <v>-4.2274</v>
+        <v>-4.7725</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.75</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2462</v>
+        <v>-0.2684</v>
       </c>
       <c r="J213" t="n">
-        <v>-5.6626</v>
+        <v>-6.1732</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.75</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2462</v>
+        <v>-0.2684</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.6626</v>
+        <v>-6.1732</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.61</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.376</v>
+        <v>-0.3939</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.648</v>
+        <v>-9.059699999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.46</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5163</v>
+        <v>-0.526</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.8749</v>
+        <v>-12.098</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.51</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1143</v>
+        <v>1.0829</v>
       </c>
       <c r="J217" t="n">
-        <v>25.6289</v>
+        <v>24.9067</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.49</v>
       </c>
       <c r="I218" t="n">
-        <v>1.0903</v>
+        <v>1.0562</v>
       </c>
       <c r="J218" t="n">
-        <v>25.0769</v>
+        <v>24.2926</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.48</v>
       </c>
       <c r="I219" t="n">
-        <v>1.0782</v>
+        <v>1.0423</v>
       </c>
       <c r="J219" t="n">
-        <v>24.7986</v>
+        <v>23.9729</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.37</v>
       </c>
       <c r="I220" t="n">
-        <v>0.9066</v>
+        <v>0.8606</v>
       </c>
       <c r="J220" t="n">
-        <v>20.8518</v>
+        <v>19.7938</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.22</v>
       </c>
       <c r="I221" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5593</v>
       </c>
       <c r="J221" t="n">
-        <v>13.018</v>
+        <v>12.8639</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.8</v>
       </c>
       <c r="I222" t="n">
-        <v>1.4956</v>
+        <v>1.4827</v>
       </c>
       <c r="J222" t="n">
-        <v>31.4076</v>
+        <v>31.1367</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.48</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1026</v>
+        <v>1.0647</v>
       </c>
       <c r="J223" t="n">
-        <v>23.1546</v>
+        <v>22.3587</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.03</v>
       </c>
       <c r="I224" t="n">
-        <v>0.0698</v>
+        <v>0.0939</v>
       </c>
       <c r="J224" t="n">
-        <v>1.4658</v>
+        <v>1.9719</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.0634</v>
+        <v>-0.0439</v>
       </c>
       <c r="J225" t="n">
-        <v>-1.3314</v>
+        <v>-0.9219000000000001</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.99</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1183</v>
+        <v>-0.1037</v>
       </c>
       <c r="J226" t="n">
-        <v>-2.4843</v>
+        <v>-2.1777</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.1</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2803</v>
+        <v>0.2772</v>
       </c>
       <c r="J227" t="n">
-        <v>5.8863</v>
+        <v>5.8212</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1</v>
       </c>
       <c r="I228" t="n">
-        <v>0.0231</v>
+        <v>0.0166</v>
       </c>
       <c r="J228" t="n">
-        <v>0.4851</v>
+        <v>0.3486</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.87</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1549</v>
+        <v>-0.1709</v>
       </c>
       <c r="J229" t="n">
-        <v>-3.2529</v>
+        <v>-3.5889</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.76</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2653</v>
+        <v>-0.281</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.5713</v>
+        <v>-5.901</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.73</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2944</v>
+        <v>-0.3095</v>
       </c>
       <c r="J231" t="n">
-        <v>-6.1824</v>
+        <v>-6.4995</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2568/event_2568_evp_summary.xlsx
+++ b/database/event/2568/event_2568_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.52</v>
+        <v>6.5957</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0504</v>
+        <v>1.0626</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3438</v>
+        <v>2.3989</v>
       </c>
       <c r="E2" t="n">
-        <v>6.52</v>
+        <v>6.5957</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2349</v>
+        <v>2.3431</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2851</v>
+        <v>4.2526</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4797</v>
+        <v>2.3545</v>
       </c>
       <c r="I2" t="n">
-        <v>1.339</v>
+        <v>1.322</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2851</v>
+        <v>4.2526</v>
       </c>
       <c r="K2" t="n">
         <v>125</v>
@@ -529,7 +529,7 @@
         <v>128</v>
       </c>
       <c r="M2" t="n">
-        <v>5.6241</v>
+        <v>5.5746</v>
       </c>
       <c r="N2" t="n">
         <v>253</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4447</v>
+        <v>5.3396</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8771</v>
+        <v>0.8602</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8543</v>
+        <v>1.8267</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4447</v>
+        <v>5.3396</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9453</v>
+        <v>2.9104</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4994</v>
+        <v>2.4292</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8236</v>
+        <v>4.4843</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6047</v>
+        <v>2.5178</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4994</v>
+        <v>2.4292</v>
       </c>
       <c r="K3" t="n">
         <v>125</v>
@@ -575,7 +575,7 @@
         <v>128</v>
       </c>
       <c r="M3" t="n">
-        <v>5.1041</v>
+        <v>4.946999999999999</v>
       </c>
       <c r="N3" t="n">
         <v>253</v>
@@ -584,139 +584,139 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.702</v>
+        <v>4.5937</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7575</v>
+        <v>0.74</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5162</v>
+        <v>1.4869</v>
       </c>
       <c r="E4" t="n">
-        <v>4.702</v>
+        <v>4.5937</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8266</v>
+        <v>2.7799</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8754</v>
+        <v>1.8138</v>
       </c>
       <c r="H4" t="n">
-        <v>7.731</v>
+        <v>3.9943</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1747</v>
+        <v>2.2427</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8754</v>
+        <v>1.8138</v>
       </c>
       <c r="K4" t="n">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="L4" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="M4" t="n">
-        <v>5.0501</v>
+        <v>4.0565</v>
       </c>
       <c r="N4" t="n">
-        <v>231</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6007</v>
+        <v>4.5303</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7412</v>
+        <v>0.7298</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4701</v>
+        <v>1.458</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6007</v>
+        <v>4.5303</v>
       </c>
       <c r="F5" t="n">
-        <v>2.741</v>
+        <v>2.8765</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8597</v>
+        <v>1.6538</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1493</v>
+        <v>4.357</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2406</v>
+        <v>2.4463</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8597</v>
+        <v>1.6538</v>
       </c>
       <c r="K5" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="L5" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="M5" t="n">
-        <v>4.1003</v>
+        <v>4.100099999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>155</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5214</v>
+        <v>4.468</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7284</v>
+        <v>0.7198</v>
       </c>
       <c r="D6" t="n">
-        <v>1.434</v>
+        <v>1.4296</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5214</v>
+        <v>4.468</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8296</v>
+        <v>3.6743</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6918</v>
+        <v>0.7937</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4417</v>
+        <v>7.3523</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3985</v>
+        <v>4.1281</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6918</v>
+        <v>0.7937</v>
       </c>
       <c r="K6" t="n">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="L6" t="n">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="M6" t="n">
-        <v>4.0903</v>
+        <v>4.9218</v>
       </c>
       <c r="N6" t="n">
-        <v>253</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3541</v>
+        <v>4.3257</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7014</v>
+        <v>0.6969</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3579</v>
+        <v>1.3648</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3541</v>
+        <v>4.3257</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7314</v>
+        <v>2.774</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6227</v>
+        <v>1.5517</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1177</v>
+        <v>3.9721</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2235</v>
+        <v>2.2302</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6227</v>
+        <v>1.5517</v>
       </c>
       <c r="K7" t="n">
         <v>50</v>
@@ -759,7 +759,7 @@
         <v>105</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8462</v>
+        <v>3.7819</v>
       </c>
       <c r="N7" t="n">
         <v>155</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2502</v>
+        <v>3.2036</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5236</v>
+        <v>0.5161</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8554</v>
+        <v>0.8536</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2502</v>
+        <v>3.2036</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7928</v>
+        <v>2.8347</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4574</v>
+        <v>0.3689</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3204</v>
+        <v>4.2001</v>
       </c>
       <c r="I8" t="n">
-        <v>2.333</v>
+        <v>2.3582</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4574</v>
+        <v>0.3689</v>
       </c>
       <c r="K8" t="n">
         <v>45</v>
@@ -805,7 +805,7 @@
         <v>76</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7904</v>
+        <v>2.7271</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.742</v>
+        <v>2.7916</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4417</v>
+        <v>0.4497</v>
       </c>
       <c r="D9" t="n">
-        <v>0.624</v>
+        <v>0.6659</v>
       </c>
       <c r="E9" t="n">
-        <v>2.742</v>
+        <v>2.7916</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6529</v>
+        <v>2.7054</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0891</v>
+        <v>0.0862</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8586</v>
+        <v>3.7147</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0836</v>
+        <v>2.0857</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0891</v>
+        <v>0.0862</v>
       </c>
       <c r="K9" t="n">
         <v>45</v>
@@ -851,7 +851,7 @@
         <v>76</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1727</v>
+        <v>2.1719</v>
       </c>
       <c r="N9" t="n">
         <v>121</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7112</v>
+        <v>2.7643</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4368</v>
+        <v>0.4453</v>
       </c>
       <c r="D10" t="n">
-        <v>0.61</v>
+        <v>0.6535</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7112</v>
+        <v>2.7643</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8566</v>
+        <v>2.8468</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1454</v>
+        <v>-0.0825</v>
       </c>
       <c r="H10" t="n">
-        <v>4.5308</v>
+        <v>4.2455</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4466</v>
+        <v>2.3837</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1454</v>
+        <v>-0.0825</v>
       </c>
       <c r="K10" t="n">
         <v>125</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5012</v>
+        <v>2.4714</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4029</v>
+        <v>0.3981</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5144</v>
+        <v>0.5201</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5012</v>
+        <v>2.4714</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0369</v>
+        <v>2.0186</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4643</v>
+        <v>0.4528</v>
       </c>
       <c r="H11" t="n">
-        <v>2.0369</v>
+        <v>2.0186</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0999</v>
+        <v>1.1334</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4643</v>
+        <v>0.4528</v>
       </c>
       <c r="K11" t="n">
         <v>178</v>
@@ -943,7 +943,7 @@
         <v>53</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5642</v>
+        <v>1.5862</v>
       </c>
       <c r="N11" t="n">
         <v>231</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3973</v>
+        <v>2.397</v>
       </c>
       <c r="C12" t="n">
         <v>0.3862</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4671</v>
+        <v>0.4862</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3973</v>
+        <v>2.397</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5324</v>
+        <v>-0.4766</v>
       </c>
       <c r="G12" t="n">
-        <v>2.9297</v>
+        <v>2.8736</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5324</v>
+        <v>-0.4766</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2875</v>
+        <v>-0.2676</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9297</v>
+        <v>2.8736</v>
       </c>
       <c r="K12" t="n">
         <v>125</v>
@@ -989,7 +989,7 @@
         <v>128</v>
       </c>
       <c r="M12" t="n">
-        <v>2.6422</v>
+        <v>2.606</v>
       </c>
       <c r="N12" t="n">
         <v>253</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3101</v>
+        <v>2.2682</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3722</v>
+        <v>0.3654</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4274</v>
+        <v>0.4275</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3101</v>
+        <v>2.2682</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3101</v>
+        <v>2.2682</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3311</v>
+        <v>2.2682</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3311</v>
+        <v>2.2682</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3311</v>
+        <v>2.2682</v>
       </c>
       <c r="N13" t="n">
         <v>104</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9727</v>
+        <v>2.0747</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3178</v>
+        <v>0.3342</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2738</v>
+        <v>0.3393</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9727</v>
+        <v>2.0747</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6168</v>
+        <v>2.6921</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6441</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7395</v>
+        <v>3.6649</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0193</v>
+        <v>2.0577</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6441</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>178</v>
@@ -1081,7 +1081,7 @@
         <v>53</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3752</v>
+        <v>1.4403</v>
       </c>
       <c r="N14" t="n">
         <v>231</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8623</v>
+        <v>1.9689</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3</v>
+        <v>0.3172</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2236</v>
+        <v>0.2911</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8623</v>
+        <v>1.9689</v>
       </c>
       <c r="F15" t="n">
-        <v>2.719</v>
+        <v>2.7722</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8567</v>
+        <v>-0.8033</v>
       </c>
       <c r="H15" t="n">
-        <v>4.0767</v>
+        <v>3.9655</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2014</v>
+        <v>2.2265</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8567</v>
+        <v>-0.8033</v>
       </c>
       <c r="K15" t="n">
         <v>45</v>
@@ -1127,7 +1127,7 @@
         <v>76</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3447</v>
+        <v>1.4232</v>
       </c>
       <c r="N15" t="n">
         <v>121</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4398</v>
+        <v>1.4579</v>
       </c>
       <c r="C16" t="n">
-        <v>0.232</v>
+        <v>0.2349</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0312</v>
+        <v>0.0584</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4398</v>
+        <v>1.4579</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5903</v>
+        <v>2.6479</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1505</v>
+        <v>-1.19</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6521</v>
+        <v>3.4987</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9721</v>
+        <v>1.9644</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.1505</v>
+        <v>-1.19</v>
       </c>
       <c r="K16" t="n">
         <v>50</v>
@@ -1173,7 +1173,7 @@
         <v>105</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8215999999999999</v>
+        <v>0.7744</v>
       </c>
       <c r="N16" t="n">
         <v>155</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3488</v>
+        <v>1.3486</v>
       </c>
       <c r="C17" t="n">
         <v>0.2173</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0102</v>
+        <v>0.0086</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3488</v>
+        <v>1.3486</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3488</v>
+        <v>1.3486</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3488</v>
+        <v>1.3486</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3488</v>
+        <v>1.3486</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3488</v>
+        <v>1.3486</v>
       </c>
       <c r="N17" t="n">
         <v>104</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2097</v>
+        <v>1.1557</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1949</v>
+        <v>0.1862</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0735</v>
+        <v>-0.0793</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2097</v>
+        <v>1.1557</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6532</v>
+        <v>1.5607</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4435</v>
+        <v>-0.405</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6532</v>
+        <v>1.5607</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8927</v>
+        <v>0.8763</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4435</v>
+        <v>-0.405</v>
       </c>
       <c r="K18" t="n">
         <v>178</v>
@@ -1265,7 +1265,7 @@
         <v>53</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4492</v>
+        <v>0.4712999999999999</v>
       </c>
       <c r="N18" t="n">
         <v>231</v>
@@ -1274,124 +1274,124 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1453</v>
+        <v>1.0052</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1845</v>
+        <v>0.1619</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1028</v>
+        <v>-0.1479</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1453</v>
+        <v>1.0052</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1453</v>
+        <v>1.8585</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1453</v>
+        <v>1.8585</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1453</v>
+        <v>1.0435</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>115</v>
+        <v>45</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1453</v>
+        <v>0.1902000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0787</v>
+        <v>0.9634</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1738</v>
+        <v>0.1552</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1332</v>
+        <v>-0.1669</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0787</v>
+        <v>0.9634</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9837</v>
+        <v>0.9634</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.905</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9837</v>
+        <v>0.9634</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0712</v>
+        <v>0.9634</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.905</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="L20" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1661999999999999</v>
+        <v>0.9634</v>
       </c>
       <c r="N20" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0607</v>
+        <v>0.9606</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1709</v>
+        <v>0.1548</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1414</v>
+        <v>-0.1682</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0607</v>
+        <v>0.9606</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0607</v>
+        <v>0.9606</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0607</v>
+        <v>0.9606</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0607</v>
+        <v>0.9606</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0607</v>
+        <v>0.9606</v>
       </c>
       <c r="N21" t="n">
         <v>115</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9444</v>
+        <v>0.9578</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1521</v>
+        <v>0.1543</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1943</v>
+        <v>-0.1695</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9444</v>
+        <v>0.9578</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9444</v>
+        <v>1.3648</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.407</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9444</v>
+        <v>1.3648</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9444</v>
+        <v>0.7663</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.407</v>
       </c>
       <c r="K22" t="n">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9444</v>
+        <v>0.3593</v>
       </c>
       <c r="N22" t="n">
-        <v>104</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9326</v>
+        <v>0.8576</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1502</v>
+        <v>0.1382</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1997</v>
+        <v>-0.2151</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9326</v>
+        <v>0.8576</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3276</v>
+        <v>0.8576</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.395</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3276</v>
+        <v>0.8576</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7169</v>
+        <v>0.8576</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.395</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>45</v>
+        <v>104</v>
       </c>
       <c r="L23" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3219</v>
+        <v>0.8576</v>
       </c>
       <c r="N23" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9038</v>
+        <v>0.8028</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1456</v>
+        <v>0.1293</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2128</v>
+        <v>-0.2401</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9038</v>
+        <v>0.8028</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9038</v>
+        <v>0.8028</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9038</v>
+        <v>0.8028</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9038</v>
+        <v>0.8028</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9038</v>
+        <v>0.8028</v>
       </c>
       <c r="N24" t="n">
         <v>115</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.7938</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1126</v>
+        <v>0.1279</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.306</v>
+        <v>-0.2442</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.7938</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.7938</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.7938</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.7938</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.7938</v>
       </c>
       <c r="N25" t="n">
         <v>108</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.5107</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0844</v>
+        <v>0.0823</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3858</v>
+        <v>-0.3731</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.5107</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.5107</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.5107</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.5107</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.5107</v>
       </c>
       <c r="N26" t="n">
         <v>71</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5053</v>
+        <v>0.4507</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0814</v>
+        <v>0.0726</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3942</v>
+        <v>-0.4005</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5053</v>
+        <v>0.4507</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1717</v>
+        <v>0.1592</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3336</v>
+        <v>0.2915</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1717</v>
+        <v>0.1592</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0927</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3336</v>
+        <v>0.2915</v>
       </c>
       <c r="K27" t="n">
         <v>50</v>
@@ -1679,7 +1679,7 @@
         <v>105</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4263</v>
+        <v>0.3809</v>
       </c>
       <c r="N27" t="n">
         <v>155</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4508</v>
+        <v>0.3663</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0726</v>
+        <v>0.059</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.419</v>
+        <v>-0.4389</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4508</v>
+        <v>0.3663</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4508</v>
+        <v>0.3663</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4508</v>
+        <v>0.3663</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4508</v>
+        <v>0.3663</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4508</v>
+        <v>0.3663</v>
       </c>
       <c r="N28" t="n">
         <v>108</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.267</v>
+        <v>0.1898</v>
       </c>
       <c r="C29" t="n">
-        <v>0.043</v>
+        <v>0.0306</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5027</v>
+        <v>-0.5193</v>
       </c>
       <c r="E29" t="n">
-        <v>0.267</v>
+        <v>0.1898</v>
       </c>
       <c r="F29" t="n">
-        <v>0.267</v>
+        <v>0.1898</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.267</v>
+        <v>0.1898</v>
       </c>
       <c r="I29" t="n">
-        <v>0.267</v>
+        <v>0.1898</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.267</v>
+        <v>0.1898</v>
       </c>
       <c r="N29" t="n">
         <v>71</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0155</v>
+        <v>-0.0344</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0025</v>
+        <v>-0.0055</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6171</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0155</v>
+        <v>-0.0344</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0155</v>
+        <v>-0.0344</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0155</v>
+        <v>-0.0344</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0155</v>
+        <v>-0.0344</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0155</v>
+        <v>-0.0344</v>
       </c>
       <c r="N30" t="n">
         <v>115</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0414</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0067</v>
+        <v>-0.0158</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.643</v>
+        <v>-0.6505</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0414</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0414</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0414</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0414</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0414</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="N31" t="n">
         <v>104</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1062</v>
+        <v>-0.1069</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0171</v>
+        <v>-0.0172</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6725</v>
+        <v>-0.6545</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1062</v>
+        <v>-0.1069</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1062</v>
+        <v>-0.1069</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1062</v>
+        <v>-0.1069</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1062</v>
+        <v>-0.1069</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1062</v>
+        <v>-0.1069</v>
       </c>
       <c r="N32" t="n">
         <v>115</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.1341</v>
+        <v>-0.1521</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0216</v>
+        <v>-0.0245</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6852</v>
+        <v>-0.6751</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.1341</v>
+        <v>-0.1521</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1341</v>
+        <v>-0.1521</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1341</v>
+        <v>-0.1521</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1341</v>
+        <v>-0.1521</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.1341</v>
+        <v>-0.1521</v>
       </c>
       <c r="N33" t="n">
         <v>71</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.2952</v>
+        <v>-0.2685</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0476</v>
+        <v>-0.0433</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7586000000000001</v>
+        <v>-0.7281</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.2952</v>
+        <v>-0.2685</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2952</v>
+        <v>-0.2685</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2952</v>
+        <v>-0.2685</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2952</v>
+        <v>-0.2685</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2952</v>
+        <v>-0.2685</v>
       </c>
       <c r="N34" t="n">
         <v>104</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3004</v>
+        <v>-0.3185</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0484</v>
+        <v>-0.0513</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.761</v>
+        <v>-0.7509</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.3004</v>
+        <v>-0.3185</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3004</v>
+        <v>-0.3185</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3004</v>
+        <v>-0.3185</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3004</v>
+        <v>-0.3185</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.3004</v>
+        <v>-0.3185</v>
       </c>
       <c r="N35" t="n">
         <v>108</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.4026</v>
+        <v>-0.3685</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0649</v>
+        <v>-0.0594</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8075</v>
+        <v>-0.7737000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.4026</v>
+        <v>-0.3685</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.2709</v>
+        <v>-1.2375</v>
       </c>
       <c r="G36" t="n">
-        <v>0.8683</v>
+        <v>0.869</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2709</v>
+        <v>-1.2375</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6863</v>
+        <v>-0.6948</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8683</v>
+        <v>0.869</v>
       </c>
       <c r="K36" t="n">
         <v>50</v>
@@ -2093,7 +2093,7 @@
         <v>105</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1819999999999999</v>
+        <v>0.1742</v>
       </c>
       <c r="N36" t="n">
         <v>155</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.4516</v>
+        <v>-0.5036</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0728</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8298</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.4516</v>
+        <v>-0.5036</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.4516</v>
+        <v>-0.5036</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.4516</v>
+        <v>-0.5036</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4516</v>
+        <v>-0.5036</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.4516</v>
+        <v>-0.5036</v>
       </c>
       <c r="N37" t="n">
         <v>108</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.7008</v>
+        <v>-0.6625</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1129</v>
+        <v>-0.1067</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9432</v>
+        <v>-0.9076</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.7008</v>
+        <v>-0.6625</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.7008</v>
+        <v>-0.6625</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.7008</v>
+        <v>-0.6625</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.7008</v>
+        <v>-0.6625</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7008</v>
+        <v>-0.6625</v>
       </c>
       <c r="N38" t="n">
         <v>71</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.9341</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1462</v>
+        <v>-0.1505</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0375</v>
+        <v>-1.0313</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.9341</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.9341</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.9341</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.9341</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.9341</v>
       </c>
       <c r="N39" t="n">
         <v>108</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3406</v>
+        <v>-1.3343</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.216</v>
+        <v>-0.215</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2345</v>
+        <v>-1.2136</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3406</v>
+        <v>-1.3343</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3406</v>
+        <v>-1.3343</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3406</v>
+        <v>-1.3343</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3406</v>
+        <v>-1.3343</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3406</v>
+        <v>-1.3343</v>
       </c>
       <c r="N40" t="n">
         <v>71</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.5481</v>
+        <v>-3.3336</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5716</v>
+        <v>-0.537</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.2394</v>
+        <v>-2.1244</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.5481</v>
+        <v>-3.3336</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.7826</v>
+        <v>-2.5918</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.7655</v>
+        <v>-0.7418</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.7826</v>
+        <v>-2.5918</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.5026</v>
+        <v>-1.4552</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.7655</v>
+        <v>-0.7418</v>
       </c>
       <c r="K41" t="n">
         <v>178</v>
@@ -2323,7 +2323,7 @@
         <v>53</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.2681</v>
+        <v>-2.197</v>
       </c>
       <c r="N41" t="n">
         <v>231</v>
@@ -2429,10 +2429,10 @@
         <v>1.12</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3902</v>
+        <v>0.3539</v>
       </c>
       <c r="J2" t="n">
-        <v>8.5844</v>
+        <v>7.7858</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3273</v>
+        <v>-0.3132</v>
       </c>
       <c r="J3" t="n">
-        <v>-7.2006</v>
+        <v>-6.8904</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.62</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3898</v>
+        <v>-0.3781</v>
       </c>
       <c r="J4" t="n">
-        <v>-8.5756</v>
+        <v>-8.318199999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.62</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3898</v>
+        <v>-0.3781</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.5756</v>
+        <v>-8.318199999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.52</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4783</v>
+        <v>-0.4741</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.5226</v>
+        <v>-10.4302</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.75</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5309</v>
+        <v>1.5615</v>
       </c>
       <c r="J7" t="n">
-        <v>33.6798</v>
+        <v>34.353</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.32</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7739</v>
+        <v>0.7548</v>
       </c>
       <c r="J8" t="n">
-        <v>17.0258</v>
+        <v>16.6056</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.32</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7739</v>
+        <v>0.7548</v>
       </c>
       <c r="J9" t="n">
-        <v>17.0258</v>
+        <v>16.6056</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.27</v>
       </c>
       <c r="I10" t="n">
-        <v>0.675</v>
+        <v>0.6512</v>
       </c>
       <c r="J10" t="n">
-        <v>14.85</v>
+        <v>14.3264</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1146</v>
+        <v>0.0902</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5212</v>
+        <v>1.9844</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.23</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4719</v>
+        <v>0.4133</v>
       </c>
       <c r="J12" t="n">
-        <v>14.157</v>
+        <v>12.399</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.11</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2631</v>
+        <v>0.2168</v>
       </c>
       <c r="J13" t="n">
-        <v>7.893</v>
+        <v>6.504</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.08</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2048</v>
+        <v>0.1648</v>
       </c>
       <c r="J14" t="n">
-        <v>6.144</v>
+        <v>4.944</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.97</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0622</v>
+        <v>-0.0486</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.866</v>
+        <v>-1.458</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.88</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.174</v>
+        <v>-0.1535</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.22</v>
+        <v>-4.605</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.32</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8361</v>
+        <v>0.8128</v>
       </c>
       <c r="J17" t="n">
-        <v>25.083</v>
+        <v>24.384</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7084</v>
+        <v>0.6753</v>
       </c>
       <c r="J18" t="n">
-        <v>21.252</v>
+        <v>20.259</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3586</v>
+        <v>0.3176</v>
       </c>
       <c r="J19" t="n">
-        <v>10.758</v>
+        <v>9.528</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.84</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5018</v>
+        <v>-0.4598</v>
       </c>
       <c r="J20" t="n">
-        <v>-15.054</v>
+        <v>-13.794</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.68</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8599</v>
+        <v>-0.8411999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>-25.797</v>
+        <v>-25.236</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.01</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0851</v>
+        <v>0.066</v>
       </c>
       <c r="J22" t="n">
-        <v>2.0424</v>
+        <v>1.584</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.9</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1299</v>
+        <v>-0.1147</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.1176</v>
+        <v>-2.7528</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.72</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3095</v>
+        <v>-0.2927</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.428</v>
+        <v>-7.0248</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.7</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.328</v>
+        <v>-0.3119</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.872</v>
+        <v>-7.4856</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3372</v>
+        <v>-0.3215</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.0928</v>
+        <v>-7.716</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.41</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8154</v>
+        <v>0.802</v>
       </c>
       <c r="J27" t="n">
-        <v>19.5696</v>
+        <v>19.248</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.35</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7315</v>
+        <v>0.7198</v>
       </c>
       <c r="J28" t="n">
-        <v>17.556</v>
+        <v>17.2752</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.33</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7032</v>
+        <v>0.6924</v>
       </c>
       <c r="J29" t="n">
-        <v>16.8768</v>
+        <v>16.6176</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.24</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5715</v>
+        <v>0.5667</v>
       </c>
       <c r="J30" t="n">
-        <v>13.716</v>
+        <v>13.6008</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.17</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4576</v>
+        <v>0.4336</v>
       </c>
       <c r="J31" t="n">
-        <v>10.9824</v>
+        <v>10.4064</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.5</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6017</v>
+        <v>0.5665</v>
       </c>
       <c r="J32" t="n">
-        <v>18.051</v>
+        <v>16.995</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1542</v>
+        <v>0.1171</v>
       </c>
       <c r="J33" t="n">
-        <v>4.626</v>
+        <v>3.513</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.0648</v>
       </c>
       <c r="J34" t="n">
-        <v>2.697</v>
+        <v>1.944</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.79</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2652</v>
+        <v>-0.2458</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.956</v>
+        <v>-7.374</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.75</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3038</v>
+        <v>-0.2863</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.114000000000001</v>
+        <v>-8.589</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5279</v>
       </c>
       <c r="J37" t="n">
-        <v>15.045</v>
+        <v>15.837</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.15</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2601</v>
+        <v>0.2468</v>
       </c>
       <c r="J38" t="n">
-        <v>7.803</v>
+        <v>7.404</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1266</v>
+        <v>0.1127</v>
       </c>
       <c r="J39" t="n">
-        <v>3.798</v>
+        <v>3.381</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1055</v>
+        <v>-0.0878</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.165</v>
+        <v>-2.634</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.89</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1651</v>
+        <v>-0.1448</v>
       </c>
       <c r="J41" t="n">
-        <v>-4.953</v>
+        <v>-4.344</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.09</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2824</v>
+        <v>0.2381</v>
       </c>
       <c r="J42" t="n">
-        <v>6.2128</v>
+        <v>5.2382</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.86</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1754</v>
+        <v>-0.1588</v>
       </c>
       <c r="J43" t="n">
-        <v>-3.8588</v>
+        <v>-3.4936</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.77</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2635</v>
+        <v>-0.2456</v>
       </c>
       <c r="J44" t="n">
-        <v>-5.797</v>
+        <v>-5.4032</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.74</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2917</v>
+        <v>-0.2743</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.4174</v>
+        <v>-6.0346</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.6</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4193</v>
+        <v>-0.4094</v>
       </c>
       <c r="J46" t="n">
-        <v>-9.224600000000001</v>
+        <v>-9.0068</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.53</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9761</v>
+        <v>0.9636</v>
       </c>
       <c r="J47" t="n">
-        <v>21.4742</v>
+        <v>21.1992</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.48</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9093</v>
+        <v>0.8959</v>
       </c>
       <c r="J48" t="n">
-        <v>20.0046</v>
+        <v>19.7098</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.39</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7862</v>
+        <v>0.7736</v>
       </c>
       <c r="J49" t="n">
-        <v>17.2964</v>
+        <v>17.0192</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.2</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5067</v>
+        <v>0.4989</v>
       </c>
       <c r="J50" t="n">
-        <v>11.1474</v>
+        <v>10.9758</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.96</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2242</v>
+        <v>-0.1918</v>
       </c>
       <c r="J51" t="n">
-        <v>-4.9324</v>
+        <v>-4.2196</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.38</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7982</v>
+        <v>0.7822</v>
       </c>
       <c r="J52" t="n">
-        <v>23.946</v>
+        <v>23.466</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.24</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5864</v>
+        <v>0.5756</v>
       </c>
       <c r="J53" t="n">
-        <v>17.592</v>
+        <v>17.268</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.15</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4367</v>
+        <v>0.4024</v>
       </c>
       <c r="J54" t="n">
-        <v>13.101</v>
+        <v>12.072</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0243</v>
+        <v>-0.0189</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.729</v>
+        <v>-0.5669999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.97</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1622</v>
+        <v>-0.1306</v>
       </c>
       <c r="J56" t="n">
-        <v>-4.866</v>
+        <v>-3.918</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.31</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5716</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>17.148</v>
+        <v>16.377</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.26</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5123</v>
+        <v>0.4789</v>
       </c>
       <c r="J58" t="n">
-        <v>15.369</v>
+        <v>14.367</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.86</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1893</v>
+        <v>-0.1688</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.679</v>
+        <v>-5.064</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.86</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1893</v>
+        <v>-0.1688</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.679</v>
+        <v>-5.064</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.62</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4181</v>
+        <v>-0.4096</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.543</v>
+        <v>-12.288</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.71</v>
       </c>
       <c r="I62" t="n">
-        <v>1.2155</v>
+        <v>1.2129</v>
       </c>
       <c r="J62" t="n">
-        <v>27.9565</v>
+        <v>27.8967</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.51</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9542</v>
+        <v>0.9409</v>
       </c>
       <c r="J63" t="n">
-        <v>21.9466</v>
+        <v>21.6407</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.43</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.8312</v>
       </c>
       <c r="J64" t="n">
-        <v>19.4419</v>
+        <v>19.1176</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.24</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5677</v>
       </c>
       <c r="J65" t="n">
-        <v>13.1813</v>
+        <v>13.0571</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.53</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.1977</v>
+        <v>-1.2306</v>
       </c>
       <c r="J66" t="n">
-        <v>-27.5471</v>
+        <v>-28.3038</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.13</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3631</v>
+        <v>0.3148</v>
       </c>
       <c r="J67" t="n">
-        <v>8.3513</v>
+        <v>7.2404</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.92</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1073</v>
+        <v>-0.0931</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.4679</v>
+        <v>-2.1413</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.78</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2542</v>
+        <v>-0.2362</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.8466</v>
+        <v>-5.4326</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.68</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3474</v>
+        <v>-0.3322</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.9902</v>
+        <v>-7.6406</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4548</v>
+        <v>-0.4486</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.4604</v>
+        <v>-10.3178</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.41</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8148</v>
+        <v>0.7744</v>
       </c>
       <c r="J72" t="n">
-        <v>21.9996</v>
+        <v>20.9088</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.09</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2607</v>
+        <v>0.2144</v>
       </c>
       <c r="J73" t="n">
-        <v>7.0389</v>
+        <v>5.7888</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.74</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2986</v>
+        <v>-0.2806</v>
       </c>
       <c r="J74" t="n">
-        <v>-8.062200000000001</v>
+        <v>-7.5762</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.65</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3816</v>
+        <v>-0.3687</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.3032</v>
+        <v>-9.9549</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.5</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5131</v>
+        <v>-0.515</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.8537</v>
+        <v>-13.905</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.4</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9426</v>
+        <v>0.931</v>
       </c>
       <c r="J77" t="n">
-        <v>25.4502</v>
+        <v>25.137</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.34</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8273</v>
+        <v>0.8058</v>
       </c>
       <c r="J78" t="n">
-        <v>22.3371</v>
+        <v>21.7566</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.32</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.7638</v>
       </c>
       <c r="J79" t="n">
-        <v>21.2706</v>
+        <v>20.6226</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.21</v>
       </c>
       <c r="I80" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5316</v>
       </c>
       <c r="J80" t="n">
-        <v>15.228</v>
+        <v>14.3532</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.87</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4625</v>
+        <v>-0.4228</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.4875</v>
+        <v>-11.4156</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.33</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7103</v>
+        <v>0.6679</v>
       </c>
       <c r="J82" t="n">
-        <v>17.7575</v>
+        <v>16.6975</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.06</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2102</v>
+        <v>0.1706</v>
       </c>
       <c r="J83" t="n">
-        <v>5.255</v>
+        <v>4.265</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.76</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2747</v>
+        <v>-0.2566</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.8675</v>
+        <v>-6.415</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.55</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4652</v>
+        <v>-0.4604</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.63</v>
+        <v>-11.51</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.45</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5514</v>
+        <v>-0.5582</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.785</v>
+        <v>-13.955</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.7</v>
       </c>
       <c r="I87" t="n">
-        <v>1.3473</v>
+        <v>1.3693</v>
       </c>
       <c r="J87" t="n">
-        <v>33.6825</v>
+        <v>34.2325</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.28</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7004</v>
+        <v>0.6756</v>
       </c>
       <c r="J88" t="n">
-        <v>17.51</v>
+        <v>16.89</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.26</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6602</v>
+        <v>0.6339</v>
       </c>
       <c r="J89" t="n">
-        <v>16.505</v>
+        <v>15.8475</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.13</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3707</v>
+        <v>0.3385</v>
       </c>
       <c r="J90" t="n">
-        <v>9.2675</v>
+        <v>8.4625</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.11</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3205</v>
+        <v>0.2886</v>
       </c>
       <c r="J91" t="n">
-        <v>8.012499999999999</v>
+        <v>7.215</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.37</v>
       </c>
       <c r="I92" t="n">
-        <v>0.492</v>
+        <v>0.4242</v>
       </c>
       <c r="J92" t="n">
-        <v>11.316</v>
+        <v>9.756600000000001</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.31</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4264</v>
+        <v>0.3623</v>
       </c>
       <c r="J93" t="n">
-        <v>9.8072</v>
+        <v>8.3329</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.23</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3355</v>
+        <v>0.2787</v>
       </c>
       <c r="J94" t="n">
-        <v>7.7165</v>
+        <v>6.4101</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.05</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0949</v>
+        <v>0.0707</v>
       </c>
       <c r="J95" t="n">
-        <v>2.1827</v>
+        <v>1.6261</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1135</v>
+        <v>-0.0958</v>
       </c>
       <c r="J96" t="n">
-        <v>-2.6105</v>
+        <v>-2.2034</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.26</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4266</v>
+        <v>0.4276</v>
       </c>
       <c r="J97" t="n">
-        <v>9.8118</v>
+        <v>9.8348</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2782</v>
+        <v>0.2647</v>
       </c>
       <c r="J98" t="n">
-        <v>6.3986</v>
+        <v>6.0881</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.84</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2083</v>
+        <v>-0.1878</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.7909</v>
+        <v>-4.3194</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.83</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2185</v>
+        <v>-0.1981</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.0255</v>
+        <v>-4.5563</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.72</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3255</v>
+        <v>-0.3089</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.4865</v>
+        <v>-7.1047</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.26</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5595</v>
+        <v>0.5033</v>
       </c>
       <c r="J102" t="n">
-        <v>13.9875</v>
+        <v>12.5825</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.93</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1058</v>
+        <v>-0.0902</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.645</v>
+        <v>-2.255</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.9</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1401</v>
+        <v>-0.1222</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.5025</v>
+        <v>-3.055</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.77</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2736</v>
+        <v>-0.2545</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.84</v>
+        <v>-6.3625</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.71</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3304</v>
+        <v>-0.3139</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.26</v>
+        <v>-7.8475</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.77</v>
       </c>
       <c r="I107" t="n">
-        <v>1.4666</v>
+        <v>1.5003</v>
       </c>
       <c r="J107" t="n">
-        <v>36.665</v>
+        <v>37.5075</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.58</v>
       </c>
       <c r="I108" t="n">
-        <v>1.2168</v>
+        <v>1.2329</v>
       </c>
       <c r="J108" t="n">
-        <v>30.42</v>
+        <v>30.8225</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.11</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3385</v>
+        <v>0.3046</v>
       </c>
       <c r="J109" t="n">
-        <v>8.4625</v>
+        <v>7.615</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.78</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.6681</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="J110" t="n">
-        <v>-16.7025</v>
+        <v>-15.915</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.68</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.8844</v>
+        <v>-0.8722</v>
       </c>
       <c r="J111" t="n">
-        <v>-22.11</v>
+        <v>-21.805</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>0.8</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.2038</v>
+        <v>-0.1874</v>
       </c>
       <c r="J112" t="n">
-        <v>-4.076</v>
+        <v>-3.748</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.75</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2563</v>
+        <v>-0.2428</v>
       </c>
       <c r="J113" t="n">
-        <v>-5.126</v>
+        <v>-4.856</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.64</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3614</v>
+        <v>-0.3521</v>
       </c>
       <c r="J114" t="n">
-        <v>-7.228</v>
+        <v>-7.042</v>
       </c>
     </row>
     <row r="115">
@@ -6989,10 +6989,10 @@
         <v>0.42</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5526</v>
+        <v>-0.5571</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.052</v>
+        <v>-11.142</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.86</v>
       </c>
       <c r="I117" t="n">
-        <v>1.5066</v>
+        <v>1.5386</v>
       </c>
       <c r="J117" t="n">
-        <v>30.132</v>
+        <v>30.772</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.52</v>
       </c>
       <c r="I118" t="n">
-        <v>1.0889</v>
+        <v>1.1056</v>
       </c>
       <c r="J118" t="n">
-        <v>21.778</v>
+        <v>22.112</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.51</v>
       </c>
       <c r="I119" t="n">
-        <v>1.0761</v>
+        <v>1.0921</v>
       </c>
       <c r="J119" t="n">
-        <v>21.522</v>
+        <v>21.842</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.48</v>
       </c>
       <c r="I120" t="n">
-        <v>1.0367</v>
+        <v>1.0487</v>
       </c>
       <c r="J120" t="n">
-        <v>20.734</v>
+        <v>20.974</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.06</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1548</v>
+        <v>0.1239</v>
       </c>
       <c r="J121" t="n">
-        <v>3.096</v>
+        <v>2.478</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.52</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1477</v>
+        <v>1.1616</v>
       </c>
       <c r="J122" t="n">
-        <v>29.8402</v>
+        <v>30.2016</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.31</v>
       </c>
       <c r="I123" t="n">
-        <v>0.788</v>
+        <v>0.761</v>
       </c>
       <c r="J123" t="n">
-        <v>20.488</v>
+        <v>19.786</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.08</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2674</v>
+        <v>0.2344</v>
       </c>
       <c r="J124" t="n">
-        <v>6.9524</v>
+        <v>6.0944</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.93</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2851</v>
+        <v>-0.2449</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.4126</v>
+        <v>-6.3674</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.83</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5437</v>
+        <v>-0.5042</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.1362</v>
+        <v>-13.1092</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.54</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.8985</v>
       </c>
       <c r="J127" t="n">
-        <v>24.466</v>
+        <v>23.361</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.06</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1651</v>
+        <v>0.1297</v>
       </c>
       <c r="J128" t="n">
-        <v>4.2926</v>
+        <v>3.3722</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.05</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1433</v>
+        <v>0.1111</v>
       </c>
       <c r="J129" t="n">
-        <v>3.7258</v>
+        <v>2.8886</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.86</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1943</v>
+        <v>-0.1736</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.0518</v>
+        <v>-4.5136</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3692</v>
+        <v>-0.3565</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.5992</v>
+        <v>-9.269</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.46</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0407</v>
+        <v>1.0451</v>
       </c>
       <c r="J132" t="n">
-        <v>24.9768</v>
+        <v>25.0824</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.34</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8262</v>
+        <v>0.8048</v>
       </c>
       <c r="J133" t="n">
-        <v>19.8288</v>
+        <v>19.3152</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.22</v>
       </c>
       <c r="I134" t="n">
-        <v>0.5845</v>
+        <v>0.5528</v>
       </c>
       <c r="J134" t="n">
-        <v>14.028</v>
+        <v>13.2672</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.22</v>
       </c>
       <c r="I135" t="n">
-        <v>0.5845</v>
+        <v>0.5528</v>
       </c>
       <c r="J135" t="n">
-        <v>14.028</v>
+        <v>13.2672</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.93</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.303</v>
+        <v>-0.2642</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.272</v>
+        <v>-6.3408</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.23</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5384</v>
+        <v>0.4876</v>
       </c>
       <c r="J137" t="n">
-        <v>12.9216</v>
+        <v>11.7024</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.99</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0041</v>
       </c>
       <c r="J138" t="n">
-        <v>-0.2016</v>
+        <v>-0.0984</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.74</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2942</v>
+        <v>-0.2765</v>
       </c>
       <c r="J139" t="n">
-        <v>-7.0608</v>
+        <v>-6.636</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.72</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.313</v>
+        <v>-0.2959</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.512</v>
+        <v>-7.1016</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.5</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5092</v>
+        <v>-0.51</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.2208</v>
+        <v>-12.24</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.2</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5659</v>
+        <v>0.5266</v>
       </c>
       <c r="J142" t="n">
-        <v>23.2019</v>
+        <v>21.5906</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.18</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5203</v>
+        <v>0.4801</v>
       </c>
       <c r="J143" t="n">
-        <v>21.3323</v>
+        <v>19.6841</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.15</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4501</v>
+        <v>0.4093</v>
       </c>
       <c r="J144" t="n">
-        <v>18.4541</v>
+        <v>16.7813</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.13</v>
       </c>
       <c r="I145" t="n">
-        <v>0.4018</v>
+        <v>0.3615</v>
       </c>
       <c r="J145" t="n">
-        <v>16.4738</v>
+        <v>14.8215</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7598</v>
+        <v>-0.7326</v>
       </c>
       <c r="J146" t="n">
-        <v>-31.1518</v>
+        <v>-30.0366</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.28</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5472</v>
+        <v>0.4875</v>
       </c>
       <c r="J147" t="n">
-        <v>22.4352</v>
+        <v>19.9875</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.12</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2787</v>
+        <v>0.2317</v>
       </c>
       <c r="J148" t="n">
-        <v>11.4267</v>
+        <v>9.499700000000001</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.03</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0926</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J149" t="n">
-        <v>3.7966</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.99</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.0305</v>
+        <v>-0.0218</v>
       </c>
       <c r="J150" t="n">
-        <v>-1.2505</v>
+        <v>-0.8938</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.96</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.0785</v>
+        <v>-0.063</v>
       </c>
       <c r="J151" t="n">
-        <v>-3.2185</v>
+        <v>-2.583</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.82</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.1861</v>
+        <v>-0.1694</v>
       </c>
       <c r="J152" t="n">
-        <v>-3.722</v>
+        <v>-3.388</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.67</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3367</v>
+        <v>-0.3261</v>
       </c>
       <c r="J153" t="n">
-        <v>-6.734</v>
+        <v>-6.522</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.64</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3633</v>
+        <v>-0.3532</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.266</v>
+        <v>-7.064</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.52</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4669</v>
+        <v>-0.4618</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.337999999999999</v>
+        <v>-9.236000000000001</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.5</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4845</v>
+        <v>-0.481</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.69</v>
+        <v>-9.619999999999999</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.84</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8983</v>
+        <v>0.8296</v>
       </c>
       <c r="J157" t="n">
-        <v>17.966</v>
+        <v>16.592</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.73</v>
       </c>
       <c r="I158" t="n">
-        <v>0.8012</v>
+        <v>0.7317</v>
       </c>
       <c r="J158" t="n">
-        <v>16.024</v>
+        <v>14.634</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.47</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5633</v>
+        <v>0.4997</v>
       </c>
       <c r="J159" t="n">
-        <v>11.266</v>
+        <v>9.994</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.41</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5038</v>
+        <v>0.4428</v>
       </c>
       <c r="J160" t="n">
-        <v>10.076</v>
+        <v>8.856</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.3</v>
       </c>
       <c r="I161" t="n">
-        <v>0.3877</v>
+        <v>0.3327</v>
       </c>
       <c r="J161" t="n">
-        <v>7.754</v>
+        <v>6.654</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.36</v>
       </c>
       <c r="I162" t="n">
-        <v>0.8897</v>
+        <v>0.8706</v>
       </c>
       <c r="J162" t="n">
-        <v>24.9116</v>
+        <v>24.3768</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.3</v>
       </c>
       <c r="I163" t="n">
-        <v>0.7679</v>
+        <v>0.7395</v>
       </c>
       <c r="J163" t="n">
-        <v>21.5012</v>
+        <v>20.706</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.11</v>
       </c>
       <c r="I164" t="n">
-        <v>0.346</v>
+        <v>0.3098</v>
       </c>
       <c r="J164" t="n">
-        <v>9.688000000000001</v>
+        <v>8.6744</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.193</v>
+        <v>-0.1584</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.404</v>
+        <v>-4.4352</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.93</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2848</v>
+        <v>-0.2446</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.9744</v>
+        <v>-6.8488</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.03</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1169</v>
+        <v>0.0871</v>
       </c>
       <c r="J167" t="n">
-        <v>3.2732</v>
+        <v>2.4388</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.02</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0895</v>
+        <v>0.0646</v>
       </c>
       <c r="J168" t="n">
-        <v>2.506</v>
+        <v>1.8088</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.85</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1928</v>
+        <v>-0.1732</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.3984</v>
+        <v>-4.8496</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.82</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2234</v>
+        <v>-0.2035</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.2552</v>
+        <v>-5.698</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2433</v>
+        <v>-0.2236</v>
       </c>
       <c r="J171" t="n">
-        <v>-6.8124</v>
+        <v>-6.2608</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.46</v>
       </c>
       <c r="I172" t="n">
-        <v>0.8659</v>
+        <v>0.8239</v>
       </c>
       <c r="J172" t="n">
-        <v>25.1111</v>
+        <v>23.8931</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.09</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2461</v>
+        <v>0.1999</v>
       </c>
       <c r="J173" t="n">
-        <v>7.1369</v>
+        <v>5.7971</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2363</v>
+        <v>-0.2162</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.8527</v>
+        <v>-6.2698</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.66</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3781</v>
+        <v>-0.3652</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.9649</v>
+        <v>-10.5908</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.65</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3871</v>
+        <v>-0.375</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.2259</v>
+        <v>-10.875</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.39</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9413</v>
+        <v>0.9282</v>
       </c>
       <c r="J177" t="n">
-        <v>27.2977</v>
+        <v>26.9178</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.33</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8232</v>
+        <v>0.7991</v>
       </c>
       <c r="J178" t="n">
-        <v>23.8728</v>
+        <v>23.1739</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.18</v>
       </c>
       <c r="I179" t="n">
-        <v>0.5063</v>
+        <v>0.4694</v>
       </c>
       <c r="J179" t="n">
-        <v>14.6827</v>
+        <v>13.6126</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.17</v>
       </c>
       <c r="I180" t="n">
-        <v>0.4839</v>
+        <v>0.447</v>
       </c>
       <c r="J180" t="n">
-        <v>14.0331</v>
+        <v>12.963</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.71</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.8166</v>
+        <v>-0.7966</v>
       </c>
       <c r="J181" t="n">
-        <v>-23.6814</v>
+        <v>-23.1014</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.85</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1298</v>
+        <v>-0.105</v>
       </c>
       <c r="J182" t="n">
-        <v>-2.4662</v>
+        <v>-1.995</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.72</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2737</v>
+        <v>-0.2605</v>
       </c>
       <c r="J183" t="n">
-        <v>-5.2003</v>
+        <v>-4.9495</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.53</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.4483</v>
+        <v>-0.4436</v>
       </c>
       <c r="J184" t="n">
-        <v>-8.5177</v>
+        <v>-8.4284</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.39</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.5714</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="J185" t="n">
-        <v>-10.8566</v>
+        <v>-10.9839</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.32</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6338</v>
+        <v>-0.6504</v>
       </c>
       <c r="J186" t="n">
-        <v>-12.0422</v>
+        <v>-12.3576</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.78</v>
       </c>
       <c r="I187" t="n">
-        <v>1.4068</v>
+        <v>1.4332</v>
       </c>
       <c r="J187" t="n">
-        <v>26.7292</v>
+        <v>27.2308</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.58</v>
       </c>
       <c r="I188" t="n">
-        <v>1.162</v>
+        <v>1.1808</v>
       </c>
       <c r="J188" t="n">
-        <v>22.078</v>
+        <v>22.4352</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.48</v>
       </c>
       <c r="I189" t="n">
-        <v>1.0349</v>
+        <v>1.0478</v>
       </c>
       <c r="J189" t="n">
-        <v>19.6631</v>
+        <v>19.9082</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.41</v>
       </c>
       <c r="I190" t="n">
-        <v>0.9227</v>
+        <v>0.9214</v>
       </c>
       <c r="J190" t="n">
-        <v>17.5313</v>
+        <v>17.5066</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.31</v>
       </c>
       <c r="I191" t="n">
-        <v>0.7319</v>
+        <v>0.7159</v>
       </c>
       <c r="J191" t="n">
-        <v>13.9061</v>
+        <v>13.6021</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.82</v>
       </c>
       <c r="I192" t="n">
-        <v>1.4658</v>
+        <v>1.495</v>
       </c>
       <c r="J192" t="n">
-        <v>30.7818</v>
+        <v>31.395</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.78</v>
       </c>
       <c r="I193" t="n">
-        <v>1.4174</v>
+        <v>1.4436</v>
       </c>
       <c r="J193" t="n">
-        <v>29.7654</v>
+        <v>30.3156</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.67</v>
       </c>
       <c r="I194" t="n">
-        <v>1.2822</v>
+        <v>1.302</v>
       </c>
       <c r="J194" t="n">
-        <v>26.9262</v>
+        <v>27.342</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.05</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1303</v>
+        <v>0.1018</v>
       </c>
       <c r="J195" t="n">
-        <v>2.7363</v>
+        <v>2.1378</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.91</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3912</v>
+        <v>-0.3576</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.215199999999999</v>
+        <v>-7.5096</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.98</v>
       </c>
       <c r="I197" t="n">
-        <v>0.0027</v>
+        <v>0.0212</v>
       </c>
       <c r="J197" t="n">
-        <v>0.0567</v>
+        <v>0.4452</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.89</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1231</v>
+        <v>-0.107</v>
       </c>
       <c r="J198" t="n">
-        <v>-2.5851</v>
+        <v>-2.247</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.73</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2908</v>
+        <v>-0.2768</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.1068</v>
+        <v>-5.8128</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.59</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4147</v>
+        <v>-0.4048</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.7087</v>
+        <v>-8.5008</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.31</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6584</v>
+        <v>-0.6819</v>
       </c>
       <c r="J201" t="n">
-        <v>-13.8264</v>
+        <v>-14.3199</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.07</v>
       </c>
       <c r="I202" t="n">
-        <v>0.2138</v>
+        <v>0.1713</v>
       </c>
       <c r="J202" t="n">
-        <v>5.5588</v>
+        <v>4.4538</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0162</v>
+        <v>0.0114</v>
       </c>
       <c r="J203" t="n">
-        <v>0.4212</v>
+        <v>0.2964</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.85</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.192</v>
+        <v>-0.1726</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.992</v>
+        <v>-4.4876</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.85</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.192</v>
+        <v>-0.1726</v>
       </c>
       <c r="J205" t="n">
-        <v>-4.992</v>
+        <v>-4.4876</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.7</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3376</v>
+        <v>-0.3216</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.7776</v>
+        <v>-8.361599999999999</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.91</v>
       </c>
       <c r="I207" t="n">
-        <v>1.6011</v>
+        <v>1.6423</v>
       </c>
       <c r="J207" t="n">
-        <v>41.6286</v>
+        <v>42.6998</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.47</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0394</v>
+        <v>1.0457</v>
       </c>
       <c r="J208" t="n">
-        <v>27.0244</v>
+        <v>27.1882</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.27</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6768</v>
+        <v>0.6525</v>
       </c>
       <c r="J209" t="n">
-        <v>17.5968</v>
+        <v>16.965</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.05</v>
       </c>
       <c r="I210" t="n">
-        <v>0.1485</v>
+        <v>0.1221</v>
       </c>
       <c r="J210" t="n">
-        <v>3.861</v>
+        <v>3.1746</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.93</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.318</v>
+        <v>-0.2815</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.268000000000001</v>
+        <v>-7.319</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.2075</v>
+        <v>-0.1923</v>
       </c>
       <c r="J212" t="n">
-        <v>-4.7725</v>
+        <v>-4.4229</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.75</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2684</v>
+        <v>-0.2548</v>
       </c>
       <c r="J213" t="n">
-        <v>-6.1732</v>
+        <v>-5.8604</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.75</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2684</v>
+        <v>-0.2548</v>
       </c>
       <c r="J214" t="n">
-        <v>-6.1732</v>
+        <v>-5.8604</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.61</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3939</v>
+        <v>-0.3831</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.059699999999999</v>
+        <v>-8.811299999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.46</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.526</v>
+        <v>-0.5273</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.098</v>
+        <v>-12.1279</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.51</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0829</v>
+        <v>1.0967</v>
       </c>
       <c r="J217" t="n">
-        <v>24.9067</v>
+        <v>25.2241</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.49</v>
       </c>
       <c r="I218" t="n">
-        <v>1.0562</v>
+        <v>1.0676</v>
       </c>
       <c r="J218" t="n">
-        <v>24.2926</v>
+        <v>24.5548</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.48</v>
       </c>
       <c r="I219" t="n">
-        <v>1.0423</v>
+        <v>1.0521</v>
       </c>
       <c r="J219" t="n">
-        <v>23.9729</v>
+        <v>24.1983</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.37</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8606</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="J220" t="n">
-        <v>19.7938</v>
+        <v>19.5569</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.22</v>
       </c>
       <c r="I221" t="n">
-        <v>0.5593</v>
+        <v>0.5325</v>
       </c>
       <c r="J221" t="n">
-        <v>12.8639</v>
+        <v>12.2475</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.8</v>
       </c>
       <c r="I222" t="n">
-        <v>1.4827</v>
+        <v>1.5151</v>
       </c>
       <c r="J222" t="n">
-        <v>31.1367</v>
+        <v>31.8171</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.48</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0647</v>
+        <v>1.0728</v>
       </c>
       <c r="J223" t="n">
-        <v>22.3587</v>
+        <v>22.5288</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.03</v>
       </c>
       <c r="I224" t="n">
-        <v>0.0939</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="J224" t="n">
-        <v>1.9719</v>
+        <v>1.5414</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.0439</v>
+        <v>-0.0387</v>
       </c>
       <c r="J225" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.8127</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.99</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1037</v>
+        <v>-0.0834</v>
       </c>
       <c r="J226" t="n">
-        <v>-2.1777</v>
+        <v>-1.7514</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.1</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2772</v>
+        <v>0.2292</v>
       </c>
       <c r="J227" t="n">
-        <v>5.8212</v>
+        <v>4.8132</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1</v>
       </c>
       <c r="I228" t="n">
-        <v>0.0166</v>
+        <v>0.0118</v>
       </c>
       <c r="J228" t="n">
-        <v>0.3486</v>
+        <v>0.2478</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.87</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1709</v>
+        <v>-0.1522</v>
       </c>
       <c r="J229" t="n">
-        <v>-3.5889</v>
+        <v>-3.1962</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.76</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.281</v>
+        <v>-0.2623</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.901</v>
+        <v>-5.5083</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.73</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3095</v>
+        <v>-0.2919</v>
       </c>
       <c r="J231" t="n">
-        <v>-6.4995</v>
+        <v>-6.1299</v>
       </c>
     </row>
   </sheetData>
